--- a/utils/monday_sprint_sprint_2026-09.xlsx
+++ b/utils/monday_sprint_sprint_2026-09.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2811" uniqueCount="728">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,7 +87,7 @@
     <t>09/02/2026</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -180,7 +180,7 @@
     <t>Alini Ferreira Ganda</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>23838</t>
@@ -237,6 +237,9 @@
     <t>05/09/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Setembro</t>
   </si>
   <si>
@@ -288,1858 +291,1816 @@
     <t>22/01/2026</t>
   </si>
   <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>36446</t>
+  </si>
+  <si>
+    <t>Inclusão de filtros no BI de Requisições</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos que sejam adicionados filtros mais específicos no BI de requisições. Precisamos adicionar uma visão de filtros que nos levem para leituras necessárias de custos com a manutenção. Filtros necessários são: Equipamento, Tipo de nota (Serviço / Compra).</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>36802</t>
+  </si>
+  <si>
+    <t>Acesso Histórico Por Funcionário</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para limitar o acesso da aba "Histórico Por Funcionário" da sistema de manutenção para os mantenedores. Deixando acessível apenas para os líderes(John, Fabiano e João) , supervisor (Robmar) e a mim e o Guilherme Ferreira do setor da manutenção Usinagem. Isso seria aqui p</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>33651</t>
+  </si>
+  <si>
+    <t>Sequencia de Pre Produtivo</t>
+  </si>
+  <si>
+    <t>Bom dia, Recebi hoje o e-mail em anexo, mas ele continua com o mesmo problema: os caracteres com acentuação não são mostrados. Por gentileza verificar. Obrigada! De: Suporte Altona &gt; Enviada em: quinta-feira, 14 de agosto de 2025 08:39 Para: Laura Herrmann Schmickler &gt;; Laura Herrmann Schmickler &gt; A</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>36689</t>
+  </si>
+  <si>
+    <t>Sistema de chamado - WMS III</t>
+  </si>
+  <si>
+    <t>Boa tarde Segue abaixo melhoria: Permitir a confirmação de coleta e entrega utilizando a tecla Enter, evitando etapas desnecessárias.</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Nova Carga de clientes.</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>36050</t>
+  </si>
+  <si>
+    <t>REGISTRO LOG DE ALTERAÇÃO DA OTF</t>
+  </si>
+  <si>
+    <t>Bom dia, Poderiam verificar pra alteração do campo abaixo ficar salvo no log de alterações: Att,</t>
+  </si>
+  <si>
+    <t>Andrew Ariel Dias</t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
+  </si>
+  <si>
+    <t>36338</t>
+  </si>
+  <si>
+    <t>Listagem de CPCs do cliente Minera San Cristóbal com a margem de Contribuição (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde Maciel, Gentileza enviar uma lista das CPCs feitas para o cliente Minera San Cristóbal (código 21189), referente aos anos de 2024 e 2025 com suas respectivas margens de contribuição. Precisamos com urgência desse relatório para solicitação da diretoria comercial. Att.</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>35642</t>
+  </si>
+  <si>
+    <t>Rateio - Tempo Padrão de Modelos - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Srs., Estamos, mais uma vez, enfrentando problemas nos rateios dos tempos dos modelos. Em diversos modelos foram identificadas inconsistências significativas, e tomamos como referência o modelo 79704074 para exemplificar a situação. Tempo que sendo reteado pelo B.I. Tempo de foi importado p</t>
+  </si>
+  <si>
+    <t>Marcos Santos Junior</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>37001</t>
+  </si>
+  <si>
+    <t>Comparativo de horas paradas entre SMI e MES - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>36262</t>
+  </si>
+  <si>
+    <t>Melhoria | Vinculo de Atraso na Invoice</t>
+  </si>
+  <si>
+    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>35409</t>
+  </si>
+  <si>
+    <t>PAINEL DOS MANIPULADORES</t>
+  </si>
+  <si>
+    <t>Bom dia, Os operadores de manipuladores apontam porcentagens de peças executadas. Precisamos dessa informação de fácil acesso no painel de operações, igual ao dos jatos, que aparece no detalhamento do apontamento.</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>36482</t>
+  </si>
+  <si>
+    <t>Estorno para inventário</t>
+  </si>
+  <si>
+    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>36287</t>
+  </si>
+  <si>
+    <t>RATPP MOVIMENTAÇÃO DO 516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Favor criar uma pergunta na movimentação do setor 516 somente para os fluxos 100, 101, 102, 103, 113, 114, 115 e 116. "HÁ NECESSIDADE DE RATPP?" com a possibilidade de resposta "SIM" ou "NÃO". Em caso de resposta "SIM", abrir saldo para o setor 567 somente após a movimentação dos setores </t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>27/01/2026</t>
+  </si>
+  <si>
+    <t>36997</t>
+  </si>
+  <si>
+    <t>% linhas mesa redonda</t>
+  </si>
+  <si>
+    <t>Bom dia, Atualização para o chamado 36157, para melhor assertividade e confiança no apontamento de %. Seria ideal ser obrigatório a escolha de peça finalizada ou não após clicar em finalizar apontamento se SIM (finalizada 100%) se NÃO (aprece a lista para indicar a % trabalhada na peça) Luiz já cien</t>
+  </si>
+  <si>
+    <t>36730</t>
+  </si>
+  <si>
+    <t>Arvore de Ativos no sistema SMI</t>
+  </si>
+  <si>
+    <t>Olá, Necessitamos que seja incluído a arvore de ativos no sistema de manutenção de forma massiva. Temos documentos em excel com as informações necessárias para a inclusão. Att,</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Rocha Junior</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>Procedimento que envie lotes de produtos cadastrados.</t>
+  </si>
+  <si>
+    <t>36685</t>
+  </si>
+  <si>
+    <t>Apontamento Tablet - Sistemas Altona</t>
+  </si>
+  <si>
+    <t>Boa tarde, referente ao sistema de apontamento dos tablets, está ocorrendo de não aparecer as operações quando transporto os dados do apontamento feito no tablet para o Excel. Isso vem acontecendo desde que as novas operações foram adicionadas, Conseguiriam fazer esse ajuste ?</t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>35353</t>
+  </si>
+  <si>
+    <t>Criação do IROG do Tratamento Térmico - Reunião para definir o que precisa ser feito</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Precisamos que seja criado uma aba para visualização do IROG do Tratamento Térmico. Incluir o ícone nessa aba: Link do apontamento do Tratamento Térmico: https://mes.altona.com.br/KB_EAA_TOTONETFrameworkOracle/wtt000.aspx Lançar os dados que estão sendo gerados nesse apontamento para a</t>
+  </si>
+  <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>36484</t>
+  </si>
+  <si>
+    <t>Melhoria da Tela de Tickets - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia Maciel, Conforme falamos, precisamos melhorar a tela para a seleção das sequencias nos tickets, para reduzir o tempo de emissão das etiquetas. Alterando as telas abaixo, para que possamos abrir uma única vez a tela e selecionar a sequência e o ticket a ser incluído, passando para o próximo a</t>
+  </si>
+  <si>
+    <t>Vanessa Karsten</t>
+  </si>
+  <si>
+    <t>36075</t>
+  </si>
+  <si>
+    <t>Apontamento de solda</t>
+  </si>
+  <si>
+    <t>Bom dia. @Felipe, conforme conversamos; Necessário acrescentar informações de dados no app "solda conferencia consumo" Acrescentar coluna com "local de trabalho" de cada soldador, para distinção entre USE e KOMATSU. Hoje, ambos setores são denominados USE. Exemplo: Formatação das colunas I e J incor</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>36977</t>
+  </si>
+  <si>
+    <t>VALOR DO FRETE NA BASE DE CALCULO DO ICMS</t>
+  </si>
+  <si>
+    <t>Boa tarde @sistemas@ti-altona.movidesk.com; Espero que esteja bem! Poderia por gentileza colocar no sistema de faturamento um lugar para adicionarmos o valor do frete na base de c?lculo do ICMS: Atenciosamente!</t>
+  </si>
+  <si>
+    <t>Nicolas de Souza</t>
+  </si>
+  <si>
+    <t>35500</t>
+  </si>
+  <si>
+    <t>indicador de aderência</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor abrir chamado para a situação a seguir: Criar indicador de aderência de programação no sistema de manutenção Atenciosamente...</t>
+  </si>
+  <si>
+    <t>Davi Jeronimo Andrade</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>Incluir no cadastro de proposta a chamada do link (item 4.3)</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>36253</t>
+  </si>
+  <si>
+    <t>SISTEMA MAPEAMENTO DIGITAL</t>
+  </si>
+  <si>
+    <t>Boa tarde, Apenas para registro, Luiz conforme conversamos por gentileza verificar as questões abaixo, · Fotos que estão ficando preto e branco, · Se possível, quando finalizado o mapeamento na hora de visualizar ou imprimir ter duas opções. Opção 1 imprimir / visualizar com fotos (lembrando que tem</t>
+  </si>
+  <si>
+    <t>Danilo da Silva Pereira</t>
+  </si>
+  <si>
+    <t>33980</t>
+  </si>
+  <si>
+    <t>Dúvida</t>
+  </si>
+  <si>
+    <t>Qlik - Store e QVD do Comparativo de Carteira e Estoque - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Felipe, Gerar um QVD e Store dos arquivos da pasta F:\01-COMPARATIVO_CARTEIRA_DEPOSITO (as 03 abas). Cada arquivo deve ser amarrado pela "data de geração" dele.</t>
+  </si>
+  <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>36418</t>
+  </si>
+  <si>
+    <t>Geração de dados Excel - Corte pó de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor inserir na geração dos dados de improdutividade o lado que apontou, estamos com dificuldade em saber qual é o lado que apontou. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>36800</t>
+  </si>
+  <si>
+    <t>Análise Tempo médio entre falhas(MTBF)</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para analisar o tempo médio entre falhas(MTBF) pelos dados do sistema de produção, o MESS, e gere um dashboard no QlikSense na aba de indicadores.</t>
+  </si>
+  <si>
+    <t>36012</t>
+  </si>
+  <si>
+    <t>Apontamentos de Horas Acabamento</t>
+  </si>
+  <si>
+    <t>Luiz, boa tarde! Ocultar / excluir apontamentos de teste que estão aparecendo em base oficial. Sequência Modelo Cliente Unidade Negócio Liga QTDE Peso Peça Origem Apontamento Hora Início Hora Final Horas Sequência CD Operação Descrição Operação 012LR 79554315 STARA S.A. INDÚSTRIA E IMPLEMENTOS AGRÍC</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>12/01/2026</t>
+  </si>
+  <si>
+    <t>36244</t>
+  </si>
+  <si>
+    <t>Falha Sistema de Indicadores GIQ</t>
+  </si>
+  <si>
+    <t>Bom dia, pessoal! Quando teremos atualização referente a esse chamado? At.te, De: Helena Mariana Segalla Enviada em: sexta-feira, 9 de janeiro de 2026 16:47 Para: 'sistemas@ti-altona.movidesk.com' Cc: Edson João Hammermeister ; Sandro Schram Assunto: Falha Sistema de Indicadores GIQ Olá, No ano pass</t>
+  </si>
+  <si>
+    <t>Helena Mariana Segalla</t>
+  </si>
+  <si>
+    <t>37091</t>
+  </si>
+  <si>
+    <t>Aba de defeitos</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para fazer uma revisão na aba de defeitos, se possível eliminar defeitos duplicados. E ampliar a busca, por exemplo, quando digitado "BKW" só aparece a busca se ele estiver no início da frase. O ideal seria fazer uma busca mais complexa permitindo aparecer as outras opçõ</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>36756</t>
+  </si>
+  <si>
+    <t>Recusa - Altona Engenharia - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde, Devido ao novo sistema da Altona Engenharia, estamos encontrando grande dificuldade para dar entrada nas notas, pois o código do produto está vindo mesmo para todos os produtos. Em conversa com o Edson Zeferino, ele nos informou que essa informação vem diretamente do sistema e que o fatur</t>
+  </si>
+  <si>
+    <t>Talita Rodrigues Sena</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>35378</t>
+  </si>
+  <si>
+    <t>Qliksense - Aplicação Refugo</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria que fosse inserido o motivo do refugo na quarta aba, na tabela abaixo: Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Raiana Correa</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>36393</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTOS NÃO ESTÃO SENDO ANEXADOS NA ANÁLISE CRÍTICA</t>
+  </si>
+  <si>
+    <t>Bom dia! Estamos com uma situação ao preencher o formulário da análise crítica: ao tentar anexar um documento, especificamente o "PROTOCOLO DIMENSIONAL", o anexo é inserido, porém ao tentar visualizá-lo, aparece a mensagem dizendo que não é possível visualizar o arquivo. Desta forma, o anexo vai par</t>
+  </si>
+  <si>
+    <t>Rodrigo Pedroso Vargas</t>
+  </si>
+  <si>
+    <t>02/02/2026</t>
+  </si>
+  <si>
+    <t>36797</t>
+  </si>
+  <si>
+    <t>leitura entre o WMS / ERP</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel. Precisamos desenvolver um método de leitura entre o WMS e o ERP para comparação automática de saldos. A ideia é que o sistema consiga puxar o saldo físico do ERP e confrontar com o saldo de cada modelo registrado no WMS, conforme o print anexado. Qual é a intenção desse processo? Cr</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>35097</t>
+  </si>
+  <si>
+    <t>Mapeamento Digital - Ajuste no salvamento</t>
+  </si>
+  <si>
+    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
+  </si>
+  <si>
+    <t>35367</t>
+  </si>
+  <si>
+    <t>Indicadores MTTR e MDT - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>35904</t>
+  </si>
+  <si>
+    <t>Melhoria no Sistema do Tratamento Térmico - Cargas ja executadas - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor acrescentar um botão para visualizar as cargas que já foram finalizadas no forno, junto ao lado do apontamento de parada. Essa função também temos disponível no sistema antigo do tratamento térmico. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>36833</t>
+  </si>
+  <si>
+    <t>Incluir campo - Retrabalho</t>
+  </si>
+  <si>
+    <t>Bom dia Segue abaixo tela para inclusão de campo:</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>37009</t>
+  </si>
+  <si>
+    <t>Relatório estoque fornecedor (Binaar/Fiedler)</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicito a criação de um novo campo no ERP, no módulo de Materiais ou Compras, para possibilitar a geração de um relatório referente ao saldo estoque fornecedor. Em anexo, encaminho um modelo para referência.</t>
+  </si>
+  <si>
+    <t>36177</t>
+  </si>
+  <si>
+    <t>Melhorias apontamento eletrônico: Manipuladores</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos, o apontamento dos Manipuladores só precisa de mais duas coisas para tirar o papel de vez. Preciso que seja feito as seguintes alterações: - Inserir a porcentagem feita da peça no painel de produção; - Tornar as informações das paradas exclusivas do painel de paradas, trocar as aba</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Santos</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
+    <t>33489</t>
+  </si>
+  <si>
+    <t>Implementação sistema retrabalho Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>36340</t>
+  </si>
+  <si>
+    <t>Cadastro de e-mails - Sistemas Altona</t>
+  </si>
+  <si>
+    <t>Boa tarde pessoal, Estamos desenvolvendo o sistema Gestão de ações juntamente com o TI, e surgiu um novo problema. Utilizamos o cadastro de usuários dos sistemas Altona para encontrar e enviar e-mail automáticos de cobrança. Porém nem todos os usuários estão com esse e-mail cadastrado (o meu por exe</t>
+  </si>
+  <si>
+    <t>Matheus Gonçalves</t>
+  </si>
+  <si>
+    <t>36780</t>
+  </si>
+  <si>
+    <t>Acessos anônimos</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos bloquear os acessos anônimos no sistema, mesmo que para consulta. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>36009</t>
+  </si>
+  <si>
+    <t>CONTROLE DE PROCEDIMENTOS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar novos controles para a coluna "Proced. OK" na tela WCPP22PR: Criar botão nesta mesma tela com funcionalidade similar ao botão "Pendência AC": Para tanto, ao cadastrar-se a necessidade de procedimento em um determinado setor de AC na tela WACVO0501, gerar registro de finalizaçã</t>
+  </si>
+  <si>
+    <t>Oportunidade - envio do tipo da moeda estrangeira e valor</t>
+  </si>
+  <si>
+    <t>35555</t>
+  </si>
+  <si>
+    <t>Painel Desmoldagem USE</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito algumas alterações no painel de desmoldagem USE: * Tela fica piscando, acredito que esteja atualizando a todo segundo, por favor alterar para atualizar a cada 2 minutos. (Vídeo 1) * Criar um campo de "Endereço" (Figura 1), neste campo será informado o local em que a caixa está de</t>
+  </si>
+  <si>
+    <t>Lucas da Silva Machado</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>35999</t>
+  </si>
+  <si>
+    <t>Divergência no Relatório Funil Vendas 80%</t>
+  </si>
+  <si>
+    <t>Boa tarde Edson, Feliz Ano Novo!!! Conforme verificado, o processo 94/24 foi incluído no indicador de 80% em 09/01/2026, por volta das 14h30, conforme evidenciado no print abaixo. No entanto, ao gerar o relatório "Funil Vendas 80%", o processo não está sendo apresentado. Aparentemente, o relatório s</t>
+  </si>
+  <si>
+    <t>36626</t>
+  </si>
+  <si>
+    <t>Incremento ao BI "Peso por área" - Regras de Negócio</t>
+  </si>
+  <si>
+    <t>Bom dia, Felipe. Conforme falamos por ligação, preciso que seja realizado um incremento no BI de "Peso por área" para que seja possível visualizarmos o peso histórico filtrado por setor, e não apenas por grupo de etapa que é o caso atual. Anexo uma imagem do estado atual, neste gráfico eu gostaria s</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>36219</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
+  </si>
+  <si>
+    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>36121</t>
+  </si>
+  <si>
+    <t>Relatório de log e filtros de métodos de preventiva</t>
+  </si>
+  <si>
+    <t>Bom dia, Conversado pessoalmente. Att,</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
+  </si>
+  <si>
+    <t>27802</t>
+  </si>
+  <si>
+    <t>Correções no chamado 26721 - Controle na geração de Sequencias</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio, Conforme falamos pelo Teams o relatório criado para controle na geração de sequencias, que estamos avaliando continua apresentando desvios. Precisamos entender o que vem ocasionando estes desvios, o plano de ação junto da GIQ continua em aberto até conseguirmos implantar este chama</t>
+  </si>
+  <si>
+    <t>Gilsimar Carls</t>
+  </si>
+  <si>
+    <t>09/09/2024</t>
+  </si>
+  <si>
+    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
+  </si>
+  <si>
+    <t>36320</t>
+  </si>
+  <si>
+    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
+  </si>
+  <si>
+    <t>34986</t>
+  </si>
+  <si>
+    <t>Registro de inspeção</t>
+  </si>
+  <si>
+    <t>Bom dia! Favor verificar o setor 7997- reteste USE, pois quando é feita a movimentação o mesmo está puxando o registro de Partícula Magnética onde o mesmo deve registrar somente " Reteste " pois a sequência abaixo é uma peça de aço inoxidável e é realizado somente o ensaio de Liquido penetrante. Obr</t>
+  </si>
+  <si>
+    <t>Mauro Morais</t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>36906</t>
+  </si>
+  <si>
+    <t>Melhorias no sistema de coleta de assinatura das declarações de recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde! Gostaria de solicitar algumas melhorias no sistema de coleta de assinatura, conforme descrito abaixo: 1. Exibição da lista de materiais após a assinaturaApós o colaborador realizar a assinatura na tela de visualização, é necessário que o sistema também apresente a lista de materiais que f</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>36937</t>
+  </si>
+  <si>
+    <t>opção de consulta quantidade mapeamentos realizados por turno</t>
+  </si>
+  <si>
+    <t>Boa tarde Luiz Por gentileza poderia nos passar um relatório de mapeamento realizados por turno, 1°turno 5:00 até 13:30 e 2°turno das 1:30 até 22:00 Se possível já deixar essa opção no sistema seria interessante para facilitarmos a consulta. Desde já agradeço Atenciosamente.</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>36737</t>
+  </si>
+  <si>
+    <t>Ajustes no Checklist de EPI's - MPO Eletrônico</t>
+  </si>
+  <si>
+    <t>Boa tarde! No checklist de EPI's do MPO Eletrônico das máquinas DALCA, LIANCO, DELTRACTOR e CLANSMAN, assim como da Ferramentaria UPR, solicito os seguintes ajustes: 1. Na pergunta referente ao capacete, atualmente consta "Capacete Laranja". Preciso que fique somente "Capacete". 1. Adicionar uma opç</t>
+  </si>
+  <si>
+    <t>Danilo dos Santos Cavalcanti</t>
+  </si>
+  <si>
+    <t>36999</t>
+  </si>
+  <si>
+    <t>Desenvolver alerta de tempo excedido com "alarme" na tela das linhas Fast Loop e Carrossel</t>
+  </si>
+  <si>
+    <t>Prezados, Favor desenvolver alerta de tempo excedido com "alarme" na tela das linhas Fast Loop e Carrossel. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>36524</t>
+  </si>
+  <si>
+    <t>CONSULTA DE SETORES EM ABERTO DE PRÉ-PRODUTIVO</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor listar todos os setores em aberto ou que ainda não receberam saldo nas sequências em aberto no sistema PCP na tela abaixo WCPP22CP. At.te</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de proposta / item</t>
+  </si>
+  <si>
+    <t>36358</t>
+  </si>
+  <si>
+    <t>Opção botão para exclusão</t>
+  </si>
+  <si>
+    <t>32996</t>
+  </si>
+  <si>
+    <t>Implementação do Checklist no sistema de Tratamento Térmico - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
+  </si>
+  <si>
+    <t>18/07/2025</t>
+  </si>
+  <si>
+    <t>35520</t>
+  </si>
+  <si>
+    <t>Aplicativo Tratamento Térmico - Bloco de Provas - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>Nova Carga de produtos.</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>36312</t>
+  </si>
+  <si>
+    <t>Nova funcionalidade na declaração de recebimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde! Identificamos a necessidade de incluir uma nova modalidade na tela de Declaração de Recebimento. Atualmente, o sistema disponibiliza apenas as seguintes opções: Ordem de CompraConsignadoRetorno de ConsertoNo entanto, alguns documentos fiscais recebidos não se enquadram nessas categorias. </t>
+  </si>
+  <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
+    <t>35738</t>
+  </si>
+  <si>
+    <t>Melhoria apontamento de corte de canais - APONTAMENTO EM LOTE</t>
+  </si>
+  <si>
+    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
+  </si>
+  <si>
+    <t>16/12/2025</t>
+  </si>
+  <si>
+    <t>36489</t>
+  </si>
+  <si>
+    <t>Trava no sistema de pré-lista da manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia! Atualmente existe uma trava no sistema de pré-lista que impede a unificação, em uma mesma pré-lista, de itens do almoxarifado com itens químicos. No entanto, o pessoal da manutenção ainda consegue realizar essa unificação. Solicitamos que a mesma trava seja aplicada também para as solicitaç</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - cliente.</t>
+  </si>
+  <si>
+    <t>36306</t>
+  </si>
+  <si>
+    <t>Controle Desmoldagem</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor avaliar a possibilidade de termos duas informações extraídas do sistema, uma delas seria o tempo de desmoldagem de cada sequência, essa informação existe na OTF. E a outra seria a data de movimentação que ocorreu a desmoldagem. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Jackson Souza</t>
+  </si>
+  <si>
+    <t>36310</t>
+  </si>
+  <si>
+    <t>Incluir o CC. 60.300 dentro de Compras e em Consequência dentro da Gerencia Supply</t>
+  </si>
+  <si>
+    <t>Incluir o CC. 60.300 dentro de Compras e em Consequencia dentro da Gerencia Supply</t>
+  </si>
+  <si>
+    <t>Clovis Stein</t>
+  </si>
+  <si>
+    <t>36165</t>
+  </si>
+  <si>
+    <t>Incluir Coluna Fases no Sistema de Investimentos</t>
+  </si>
+  <si>
+    <t>Bom dia Edson, Consegues incluir no fluxo de caixa analitico uma coluna com o nome da fase do projeto. Na proxima semana temos reunião e preciamos desta informação até dia 26/01... Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Rafael Pereira</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>36348</t>
+  </si>
+  <si>
+    <t>Inclusão de parâmetro de exportação de notas</t>
+  </si>
+  <si>
+    <t>Boa tarde! Peço que na hora de exportar as notas para o sistema do Benner, seja adicionado mais um parâmetro para os produtos, conforme demonstrado abaixo: Estou solicitando essa inclusão pois agora temos 3 empresas dentro do Benner, e se não colocar como parâmetro a empresa, o sistema tenta puxar o</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - produto.</t>
+  </si>
+  <si>
+    <t>36352</t>
+  </si>
+  <si>
+    <t>Atualização de mínimos e máximos</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor atualizar as quantidade de estoque min e max dos itens da planilha. Att De: Rafael da Cruz Enviada em: domingo, 11 de janeiro de 2026 19:08 Para: João Carlos Fagundes Filho ; Gustavo Henrique Keunecke ; Alan Jonis da Silva Assunto: ENC: Atualização de mínimos e máximos Boa tarde Obr</t>
+  </si>
+  <si>
+    <t>Alan Jonis da Silva</t>
+  </si>
+  <si>
+    <t>Nova carga de oportunidades.</t>
+  </si>
+  <si>
+    <t>36321</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação – Notificação no Sistema de Assinatura Digital</t>
+  </si>
+  <si>
+    <t>Bom dia! Solicitamos a implementação de uma nova funcionalidade no sistema de coleta de assinatura digital das declarações de recebimento.A proposta consiste nas seguintes opções:1. Que, após o cadastramento da declaração de recebimento, seja disparado automaticamente um e‑mail ao requisitante, info</t>
+  </si>
+  <si>
+    <t>36196</t>
+  </si>
+  <si>
+    <t>Melhoria - Incluir Dt de Entrega e Referência de Atraso</t>
+  </si>
+  <si>
+    <t>Bom dia, Incluir na tela de Lançamento de Conhecimento de Frete 02 campos: * Após dada de Vencimento incluir data de entrega (obrigatória para o cfop da NF 5101 e 6101). Após o lançamento da NFm caso for desses CFOP, não permitir sair sem preencher, e notificar a pendencia. * Incluir campo "Frete De</t>
+  </si>
+  <si>
+    <t>27561</t>
+  </si>
+  <si>
+    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG (copy)</t>
+  </si>
+  <si>
+    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
+  </si>
+  <si>
+    <t>Guilherme Mendes</t>
+  </si>
+  <si>
+    <t>22/08/2024</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de oportunidades / proposta / item</t>
+  </si>
+  <si>
+    <t>35128</t>
+  </si>
+  <si>
+    <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Dando continuidade ao processo de melhoria nas conferências do estoque peço que insiras no relatório abaixo: duas colunas conforme descrição abaixo e planilha anexa: 1) Finalidade (MP/C) - esse parâmetro servirá para conferir se um produto está classificado corretamente e consequent</t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>37054</t>
+  </si>
+  <si>
+    <t>BLOQUEIO DE SETORES NO APONTAMENTO ELETRONICO - Komatsu REB VI - VII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, No apontamento eletrônico existe a aba de preenchimento ( setor ), necessitamos que quando não for preenchida o próprio sistema bloqueia o apontamento, não deixando apontar. Temos essa opção no número da cabine, se o operador não preencher a cabine o apontamento é bloqueado, Esta opção vai </t>
+  </si>
+  <si>
+    <t>Otavio Zimmermann Neto</t>
+  </si>
+  <si>
+    <t>36194</t>
+  </si>
+  <si>
+    <t>CNPJ Alfanumérico - Instrução Normativa 2.229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De: Alexandro Fernandes Correa Enviada em: terça-feira, 20 de janeiro de 2026 07:29 Para: José Carlos Emygdio ; Rubia Maiara Raasch Mota Cc: Edson João Hammermeister Assunto: ENC: [Comunicado] CNPJ Alfanumérico - Instrução Normativa 2.229 Prioridade: Alta Bom dia Para atentarmos aos nossos sistemas </t>
+  </si>
+  <si>
+    <t>36716</t>
+  </si>
+  <si>
+    <t>informação de conta bancária no debit memo</t>
+  </si>
+  <si>
+    <t>Bom dia Algumas vezes a Alstom já me questionou sobre dados bancários nos debit memos enviados, porque simplesmente não tem. No credit memo talvez não seja necessário, mas teria que ter essa informação nos debit memos, para evitar atrasos em pagamentos. Fica a sugestão. Grata</t>
+  </si>
+  <si>
+    <t>Tatiana Alves</t>
+  </si>
+  <si>
+    <t>36632</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia! Gostaria de criar um campo no ERP para cadastro de quantidade de peças por transferência (lote de transferência) Ex: Tipo de equipamento e Quantidade 1. Caixas de ferro: XX peças do modelo YYYYYY 2. Racks Stara: XX peças do modelo AAAAAA 3. Pallets: XX peças do modelo BBBBB Quem terá acesso</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>36218</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
+  </si>
+  <si>
+    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
+  </si>
+  <si>
+    <t>Procedimento que envia lotes de oportunidade cadastradas</t>
+  </si>
+  <si>
+    <t>36417</t>
+  </si>
+  <si>
+    <t>Chamado de Manilha</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme conversa feita com o Flavio, precisamos entender a estrutura de cálculo para o sistema de MRP de manilha. Compras - Manutenção - MRP manilha. Att</t>
+  </si>
+  <si>
+    <t>34073</t>
+  </si>
+  <si>
+    <t>ALTC - Adicionar ao SIGA e ajustar visual dos botões</t>
+  </si>
+  <si>
+    <t>37133</t>
+  </si>
+  <si>
+    <t>Quebra de lote para criação de pendência</t>
+  </si>
+  <si>
+    <t>boa tarde, Conforme conversado na reunião de hoje (09/03), favor liberar quebra de lote para setor da usinagem. Hoje, não há possibilidade de criar pendência sem ter que movimentar todo o lote. É importante que tenha essa possibilidade para melhorar nosso rastreio e aberturas de retrabalhos corretam</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>35753</t>
+  </si>
+  <si>
+    <t>BUG SISTEMA MAPEAMENTO DIGITAL</t>
+  </si>
+  <si>
+    <t>Boa tarde!! Em diversas situações já nos deparamos com este bug que ao iniciar um novo mapeamento, pegamos as medidas da peça pelo tablete e concluímos o mapeamento para finalizar o restante das informações na cabine, mas ao chegar na cabine e tentar abrir o mapeamento pelo Chrome (Windows) não cons</t>
+  </si>
+  <si>
+    <t>Gian Lucas Corrente</t>
+  </si>
+  <si>
+    <t>36760</t>
+  </si>
+  <si>
+    <t>B.I. Acabamento Komatsu</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Para o rateio do tempo padrão nas operações do IROG Acabamento, desconsiderar o critério da "Flag Peça Finalizada". Qualquer dúvida, estou à disposição! Atenciosamente,</t>
+  </si>
+  <si>
+    <t>36213</t>
+  </si>
+  <si>
+    <t>Alteração no sistema de manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
+  </si>
+  <si>
+    <t>36761</t>
+  </si>
+  <si>
+    <t>CONTROLE DE PRAZOS PROCEDIMENTOS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor agregar este ticket ao ticket 36009. Favor criar os seguintes pontos no sistema pré-produtivo: * Na rela TANCR011 criar um campo de data para que seja incluído a data de fechamento do item. * Na tela TACVO05 incluir campo para cadastro do prazo de procedimento (em dias): * Na tela W</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de item.</t>
+  </si>
+  <si>
+    <t>31836</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que as etapas de Saida Deposito do WMS possam ser revertidas e editadas após o processo "finalizado". * Uma vez realizado o carregamento, que seja possível , voltar e excluir NF / itens. Sugestão: selecionar os romaneios (já vinculados a NF) e excluir, voltando os Romaneios a St</t>
+  </si>
+  <si>
+    <t>22/05/2025</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>36750</t>
+  </si>
+  <si>
+    <t>ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL - Ajustes no editor de mapeamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">________________________________ De: Gian Lucas Corrente Enviado: sexta-feira, 6 de fevereiro de 2026 18:32 Para: Danilo da Silva Pereira ; Luiz Gustavo de Salles Pinho ; Sergio Schmidt Cc: Barbara Braatz Vetter Assunto: RES: ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL NA TELA “INFORMAÇÕES DO MAPEAMENTO” </t>
+  </si>
+  <si>
+    <t>Luiz Gustavo de Salles Pinho</t>
+  </si>
+  <si>
+    <t>36366</t>
+  </si>
+  <si>
+    <t>VISUALIZAÇÃO DE PORCENTAGEM E TEMPO DISPONIVEL APONTAMENTO ELETRONICO USE (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, Para melhorar visualização dos operadores, precisamos de um campo que mostre o percentual disponível e o tempo ainda disponível da peça referente ao tempo padrão. Tela para mostrar os dados solicitados após indicar sequência, caso ultrapasse o tempo disponível (padrão) retornar 0 hrs. Qua</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>31701</t>
+  </si>
+  <si>
+    <t>Extrações para IA SENAI</t>
+  </si>
+  <si>
+    <t>36220</t>
+  </si>
+  <si>
+    <t>INFORMAÇÕES SOBRE MATERIAL DO MODELO EM FTF'S DE CONJUNTO</t>
+  </si>
+  <si>
+    <t>35527</t>
+  </si>
+  <si>
+    <t>Orçamento 2025 - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Marcio Silva</t>
+  </si>
+  <si>
+    <t>36764</t>
+  </si>
+  <si>
+    <t>Falha ao salvar mapeamento</t>
+  </si>
+  <si>
+    <t>Testar e identificar possíveis falhas ao salvar o mapeamento digital, * Adicionar medidas para quando ocorrer qualquer erro no JS avisar ao usuário * Adicionar gatilhos para quando identificar que o json final está com o valor inicial forcar o js a gerar os dados</t>
+  </si>
+  <si>
+    <t>37033</t>
+  </si>
+  <si>
+    <t>WMS - tela resumo de atividade</t>
+  </si>
+  <si>
+    <t>Boa tarde! No WMS gostaria de crie uma tela resumo de atividade por área de acionamento: 1. Lista das origens 2. Ativo | Não ativo 3. Data e Hora do último Acionamento Obrigado! Obter o Outlook para iOS</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>36719</t>
+  </si>
+  <si>
+    <t>ADIÇÃO DE CAIXA DE PESQUISA</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo bem? Solicito a inclusão de uma caixa de pesquisa por nome do fornecedor para se tornar mais fácil a localização das pesagens assim como já existe a caixa de pesquisa por placa. Att.</t>
+  </si>
+  <si>
+    <t>Manuelle Teixeira Sampaio</t>
+  </si>
+  <si>
+    <t>33048</t>
+  </si>
+  <si>
+    <t>Custos FTF</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
+  </si>
+  <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
+    <t>34952</t>
+  </si>
+  <si>
+    <t>Criação Relatório BI ProfMix</t>
+  </si>
+  <si>
+    <t>Incluir no cadastro de oportunidades a chamada do link (item 3.3)</t>
+  </si>
+  <si>
+    <t>Criar procedimento que envie lotes de Oportunidades</t>
+  </si>
+  <si>
+    <t>37063</t>
+  </si>
+  <si>
+    <t>Desconto de Paradas do Tempo Produtivo</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme conversado em chamada com o Felipe, os tempos produtivos apontados para os Jatos, não estão descontando os tempos de paradas apontadas. Nesse caso acima (teste), foi apontado 5min produtivos, porem tivemos 1min de parada que não descontou do tempo produtivo. Outro chamado em andame</t>
+  </si>
+  <si>
+    <t>37019</t>
+  </si>
+  <si>
+    <t>Baixa Automática Material de Estoque por Nota Fiscal de Venda Sucata</t>
+  </si>
+  <si>
+    <t>Bom dia a todos! Sandro, Desenvolver a baixa de itens (materiais) que tenham controle de estoque automaticamente. ________________________________ De: Sandro Schram Enviadas: Quarta-feira, 04 de Março de 2026 08:40 Para: Paulo Giovani da Cruz ; Marcelo Americo Cc: Marcio Silva ; Cezar Gomes de Olive</t>
+  </si>
+  <si>
+    <t>35067</t>
+  </si>
+  <si>
+    <t>Erro IROG acabamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
+  </si>
+  <si>
+    <t>Carlos Correia</t>
+  </si>
+  <si>
+    <t>Incluir no cadastro do item da proposta a chamada do link (item 5.3)</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>36304</t>
+  </si>
+  <si>
+    <t>Solicitação de Melhorias no Sistema de Coleta de Assinaturas</t>
+  </si>
+  <si>
+    <t>Bom dia! Precisamos implementar algumas melhorias no sistema de coleta de assinatura das declarações de recebimento. Seguem os pontos identificados: Validação de NF: Implementar uma verificação para identificar se a Nota Fiscal foi emitida contra a Altona ou se passou pela portaria, garantindo que e</t>
+  </si>
+  <si>
+    <t>B.I. Acabamento - Alimentar dados retroativos</t>
+  </si>
+  <si>
+    <t>32989</t>
+  </si>
+  <si>
+    <t>IROG Tratamento Térmico no BI - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Foi conversado que, com as informações presentes hoje no sistema (disponibilidade, performance e qualidade), pode-se iniciar a implantação do IROG no BI. Em paralelo, o time da TI irá conduzir as melhorias pontuadas. Edson informou que o BI e melhorias serão atendidos em um mesmo chamado; 1</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>34335</t>
+  </si>
+  <si>
+    <t>Tempo Padrão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
+  </si>
+  <si>
+    <t>34012</t>
+  </si>
+  <si>
+    <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estamos com uma ação vinculada ao projeto Produttare e algumas frentes de implementação de indicadores na área de Manutenção. Precisamos da ajuda do time de TI para iniciarmos com um painel de indicadores com as seguintes sugestões para implementação via Qlikview. Indicador MDT (Mean down</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
+    <t>29848</t>
+  </si>
+  <si>
+    <t>Alteração da referencia de Etiqueta para Romaneio - Validação</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>36278</t>
+  </si>
+  <si>
+    <t>Altona || Estoque Consignado Binaar</t>
+  </si>
+  <si>
+    <t>Boa tarde, Edson Precisamos devolver o estoque de consignados da Binaar até dia 30/01/2026 por uma orientação do Cleber. Peço que revejas com o Sandro a possibilidade dele focar nessa tarefa para conseguirmos cumprir com a solicitação da diretoria. Obrigado</t>
+  </si>
+  <si>
+    <t>36690</t>
+  </si>
+  <si>
+    <t>Sistema de chamado - WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde Segue abaixo melhoria: Reduzir confirmações repetitivas de "sim" durante os processos de coleta e entrega, agilizando o fluxo</t>
+  </si>
+  <si>
+    <t>36871</t>
+  </si>
+  <si>
+    <t>Inventario Filial</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos de uma tela para inventário nos itens do "Estoque Fornecedor". Em conversa com o Alex, ele comentou que deve ser nessa tela. Sandro, estamos querendo implementar uma melhoria para controle de estoque, fazer a baixa desse estoque direto com o coletor padrão do Almoxarifado. E cons</t>
+  </si>
+  <si>
+    <t>ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL - Criar nova tela para tirar fotos e ajustar a grid de visualização</t>
+  </si>
+  <si>
+    <t>36668</t>
+  </si>
+  <si>
+    <t>Sistema de chamado - WMS II</t>
+  </si>
+  <si>
+    <t>37022</t>
+  </si>
+  <si>
+    <t>sistema de apontamento da lubrificação</t>
+  </si>
+  <si>
+    <t>Bom dia, precisamos inserir no sistema de manutenção um método de apontamento para os lubrificadores onde eles consigam colocar a quantidade de lubrificantes, tipo de lubrificantes e serviço. Para poder gerarmos relatórios de consumo e custos de lubrificante gasto . Podemos marcar uma reunião para a</t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>36898</t>
+  </si>
+  <si>
+    <t>Itens em falta - Criticidade do item e relatório no Sense</t>
+  </si>
+  <si>
+    <t>Bom dia, Preciso de um relatório no qliksense com lista de todos os materiais com saldo zerado no sistema. E precisamos adicionar no cadastro do material a criticidade do item, A,B,C. quando tiver essa informação ela deve estar nesse relatório junto com as peças que estão faltando. Att</t>
+  </si>
+  <si>
+    <t>35047</t>
+  </si>
+  <si>
+    <t>Atualização de aplicações</t>
+  </si>
+  <si>
+    <t>36157</t>
+  </si>
+  <si>
+    <t>APONTAMENTO LINHAS UPR (acrescentar opção de apontamento de % nas linhas UPR)</t>
+  </si>
+  <si>
+    <t>Acrescentar opção de apontamento de % nas linhas UPR, disponibilizar lista de 10 em 10%. A soma não pode ultrapassar os 100%.</t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>36475</t>
+  </si>
+  <si>
+    <t>PESO DE CONJUNTO CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar uma nova regra em CPPs de tipo Normal e Componente onde o peso de conjunto seja preenchido automaticamente utilizando a fórmula abaixo: (Peso Bruto + Peso Alimentação) x Qtde Modelos P/Placa = Peso Conjunto. Hoje esse cálculo já é feito nos formulários de análise crítica dos s</t>
+  </si>
+  <si>
+    <t>36460</t>
+  </si>
+  <si>
+    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo UInventa</t>
+  </si>
+  <si>
+    <t>Sandro, dando continuidade ao chamado 35127 identifiquei dois problemas: 1) O saldo anterior + entradas - consumo está diferente do valor apresentado no inventário (imagem 1) Imagem 1 2) O saldo do inventário em excel está diferente do relatório em PDF. NO excel ainda tem uma faixa de itens a ser li</t>
+  </si>
+  <si>
+    <t>36302</t>
+  </si>
+  <si>
+    <t>Altona || OSI - Suspensão</t>
+  </si>
+  <si>
+    <t>Bom dia! O Richard encerrou o chamado 35369 e como eu cadastrei o nome incorretamente, deixei passar. Esse chamado é uma continuação do 35369.</t>
+  </si>
+  <si>
+    <t>35731</t>
+  </si>
+  <si>
+    <t>Indicadores Moldes Moldagem USE</t>
+  </si>
+  <si>
+    <t>Bom dia. Preciso criar/adaptar um aplicativo do QlikSense. Hoje há um aplicativo que mostra as movimentações por sequência de peça, porém preciso que esse indicador seja apresentado por quantidade de moldes. Para isso, há a informação do sistema da quantidade de peças por placa de moldagem, conforme</t>
+  </si>
+  <si>
+    <t>37010</t>
+  </si>
+  <si>
+    <t>Relatório em Excel no sistema de inventário de embalagens</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicito a implementação de um relatório com comparativo saldo atual X quantidade física. pode-se utilizar como referencia o relatório existente hoje no modelo de inventário do Almoxarifado.</t>
+  </si>
+  <si>
+    <t>35747</t>
+  </si>
+  <si>
+    <t>Criar novo código de operação para o QlikSense</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos. Atualmente nós apontamos os dados da máquina Lianco (setor 1531) e Dalca (setor 1530) no sistema de Apontamento de Produção, e no QlikSense mostra exatamente os dados que apontamos, e como não apontamos uma "operação" acaba que no QlikSense não aparece código de operação. Porém is</t>
+  </si>
+  <si>
+    <t>36743</t>
+  </si>
+  <si>
+    <t>Aplicação sem dados após 06/02</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor verificar a aplicação parou de gerar os dados de auditoria depois do dia 06/02/2026. Acredito que tenha vínculo com os apontamentos de máquina, o qual sofreu alteração de sistema. Grato,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>36298</t>
+  </si>
+  <si>
+    <t>APONTAMENTO LINHAS UPR (TAXA DE ATUALIZAÇÃO)</t>
+  </si>
+  <si>
+    <t>Verificada lentidão na taxa de atualização a cada etapa/clique, apontamento linha mesa redonda.</t>
+  </si>
+  <si>
+    <t>37025</t>
+  </si>
+  <si>
+    <t>Melhorias no sistema de cadastro de matérias</t>
+  </si>
+  <si>
+    <t>Bom dia, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1.Puxar as seguintes informações tipo produto; grupo; Ressuprimentos. Conforme imagem abaixo 2. Colocar um campo de data, na opção de aprovar cadastros.</t>
+  </si>
+  <si>
+    <t>35792</t>
+  </si>
+  <si>
+    <t>Criação de campos no sistema de manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
+  </si>
+  <si>
+    <t>Vitor de Oliveira da Silva</t>
+  </si>
+  <si>
+    <t>18/12/2025</t>
+  </si>
+  <si>
+    <t>36125</t>
+  </si>
+  <si>
+    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - oportunidade.</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>36142</t>
+  </si>
+  <si>
+    <t>Incluir no relatório de aciaria o saldo em estoque de terceiro</t>
+  </si>
+  <si>
+    <t>36229</t>
+  </si>
+  <si>
+    <t>Troca de campanha forno indução</t>
+  </si>
+  <si>
+    <t>Solicito troca sistemática da troca de campanha no forno indução, Sistema semelhante ao da troca de campanha de panelas Segue local e o sistema de corridas:</t>
+  </si>
+  <si>
+    <t>34225</t>
+  </si>
+  <si>
+    <t>Correções Relatório Faturamento por Sequência - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>32079</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>04/06/2025</t>
+  </si>
+  <si>
+    <t>35550</t>
+  </si>
+  <si>
+    <t>Implementação de Índice de Qualidade de Manutenção</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estou formalizando a solicitação da implementação de uma sistemática de índice de qualidade para os serviços de manutenção. Dessa maneira precisamos implementar um sistema de Status "Baixado" ser a última etapa do processo interno de manutenção e assim que o Status for "Baixado" o sistema</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>34896</t>
+  </si>
+  <si>
+    <t>Alteração de calculo do BI</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., 1ª Alteração: Precisamos alterar o cálculo da performance conforme abaixo: O Tempo Padrão deve ser considerado por sequência e operação. Caso sejam apontados a mesma operação por mais de uma vez para a mesma sequência, o Tempo Padrão deve ser rateado entre estes apontamentos, levando</t>
+  </si>
+  <si>
+    <t>Lucas Sebold Movidesk</t>
+  </si>
+  <si>
+    <t>24/10/2025</t>
+  </si>
+  <si>
+    <t>24/04/2026</t>
+  </si>
+  <si>
+    <t>36441</t>
+  </si>
+  <si>
+    <t>Qlik | Aplicação de Reconhecimento de Receita</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza fazer o vínculo de atualização da aplicação - Logistica &gt; 2 - Reconhecimento de Receita Root/QVD/EXTRACAO/NFEDESP.qvd] - Nota fiscal Root/QVD/EXTRACAO/CPC389.qvd] - Invoice Root/QVD/EXTRACAO/CTEEMIT.qvd] - Cte (Obs: o chamado 36196 possui 02 campos novos que quando feitos precisam</t>
+  </si>
+  <si>
+    <t>36706</t>
+  </si>
+  <si>
+    <t>B.I. de Horas Extras - (ACOMPANHAMENTO DGL)</t>
+  </si>
+  <si>
+    <t>36717</t>
+  </si>
+  <si>
+    <t>DATA LIMITE PARA BAIXA DE O.S</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de implementar uma opção no sistema de manutenção, onde possa ser limitado e/ou justificado o motivo da ordem não ter sido baixada no tempo hábil. Exemplo: Peguei uma O.S. no dia 17/02/2026, com a função habilitada e definida pelo usuário, tenho o limite de dias conforme a O.S. (em</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>36375</t>
+  </si>
+  <si>
+    <t>Controle de Periodo Firme da Programacao da Carteira</t>
+  </si>
+  <si>
+    <t>Indicador de Aderencia - Carga de dados</t>
+  </si>
+  <si>
+    <t>36301</t>
+  </si>
+  <si>
+    <t>AOD - Panelas</t>
+  </si>
+  <si>
+    <t>Sistema de Apontamento de panelas deve ser no AOD igual aos demais fornos</t>
+  </si>
+  <si>
+    <t>36487</t>
+  </si>
+  <si>
+    <t>Altona || Nota de devolução de compra sem Requisição de Estoque</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Peço tua ajuda para criar uma rotina que não permita mais que notas de devolução de compra com itens de estoque sejam emitidas sem a respectiva requisição de devolução. Sugiro que ao adicionar o produto (no processo de emissão de nota), o SNB verifique se esse item é estoque (Contas</t>
+  </si>
+  <si>
+    <t>36326</t>
+  </si>
+  <si>
+    <t>Modelos com vazamento a mais de 4 anos</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza incluir a caroline.schmitt@altona.com.br no recebimento desses e-mails. Alterar a frequência para 1x na semana (todas as segundas-feiras). -----Mensagem original----- De: Modelos com vazamento a mais de 4 anos Enviada em: quinta-feira, 29 de janeiro de 2026 05:12 Para: taynara.fra</t>
+  </si>
+  <si>
+    <t>Taynara Frare</t>
+  </si>
+  <si>
+    <t>36327</t>
+  </si>
+  <si>
+    <t>Sequencias paradas no setor</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza incluir a caroline.schmitt@altona.com.br no recebimento desses e-mails. -----Mensagem original----- De: Sequencias paradas no setor Enviada em: quinta-feira, 29 de janeiro de 2026 06:50 Para: pendencias.aciaria@ Assunto: Sequencias paradas no setor Em anexo segue lista de sequenci</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>35764</t>
+  </si>
+  <si>
+    <t>Automação da lista de presença - Detalhar escopo</t>
+  </si>
+  <si>
+    <t>36245</t>
+  </si>
+  <si>
+    <t>Carregar dados no QlikSense</t>
+  </si>
+  <si>
+    <t>Bom dia, pessoal! Quando teremos atualização referente a esse chamado? At.te, De: Helena Mariana Segalla Enviada em: sexta-feira, 9 de janeiro de 2026 09:30 Para: 'sistemas@ti-altona.movidesk.com' Cc: Edson João Hammermeister ; Richard Rene Zalasik ; Sandro Schram Assunto: ENC: Carregar dados no Qli</t>
+  </si>
+  <si>
+    <t>36705</t>
+  </si>
+  <si>
+    <t>MODIFICAÇÃO NO SISTEMA DE MANUTENÇÃO</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de adicionar uma opção no sistema de manutenção, na aba de "permissões" - Adicionar um limite de ordens em andamento, como o exemplo abaixo: (além do "Limite de Paradas Permitidas", colocar o "Limite de ordens em andamento"). Aguardo retorno,</t>
+  </si>
+  <si>
+    <t>17/02/2026</t>
+  </si>
+  <si>
+    <t>36046</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Valorização de modelos</t>
+  </si>
+  <si>
+    <t>31977</t>
+  </si>
+  <si>
+    <t>Alterações no registro de moldagem via APP - Validação</t>
+  </si>
+  <si>
+    <t>36453</t>
+  </si>
+  <si>
+    <t>Divergência no Relatório Funil Vendas 80% - Acompanhamento</t>
+  </si>
+  <si>
+    <t>36398</t>
+  </si>
+  <si>
+    <t>Add opção de revisão valor de frete na CPC</t>
+  </si>
+  <si>
+    <t>36692</t>
+  </si>
+  <si>
+    <t>Sequencias de conjunto</t>
+  </si>
+  <si>
+    <t>Boa tarde, Maciel. Conforme conversamos, precisamos que as informações das sequências do conjunto sejam exibidas diretamente na tela atual do WMS. Atualmente, a consulta dessas sequências precisa ser feita por meio de outras telas, o que tem aumentado nosso tempo de análise e, consequentemente, noss</t>
+  </si>
+  <si>
+    <t>37327</t>
+  </si>
+  <si>
+    <t>Porcentagem manipuladores</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos, eu e o Douglas Garcia percebemos um erro no painel de produção dos manipuladores e na extração dos dados. A porcentagem executada está sempre aparecendo como 100%, mesmo sendo apontado porcentagens diferentes, fizemos um teste de apontamento para saber se não era erro na hora de a</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>Pendencias e retrabalhos nas ordens geradas e novas</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo.</t>
+  </si>
+  <si>
+    <t>Alterar as estruturas das tabelas de op para considerar as múltiplas modelagens, e múltiplos ambientes no sql (produção e qualidade).</t>
+  </si>
+  <si>
+    <t>Para a geração das OP’s eu considero que o melhor seria termos um plano mestre por SKU, com datas e quantidades</t>
+  </si>
+  <si>
+    <t>37151</t>
+  </si>
+  <si>
+    <t>ERRO NA SELEÇÃO DE PARADA SEM SEQUÊNCIA LINHA MESA REDONDA UPR</t>
+  </si>
+  <si>
+    <t>Bom dia, Luiz, Possível erro na seleção de parada sem sequência favor avaliar. Em anexo vídeo do apontamento da peça 590LZ que é uma peça de sequência única indicando que seria uma peça lote possível erro de cadastro da sequencia ou modelo, Qualquer dúvida a disposição;</t>
+  </si>
+  <si>
     <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>36446</t>
-  </si>
-  <si>
-    <t>Inclusão de filtros no BI de Requisições</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos que sejam adicionados filtros mais específicos no BI de requisições. Precisamos adicionar uma visão de filtros que nos levem para leituras necessárias de custos com a manutenção. Filtros necessários são: Equipamento, Tipo de nota (Serviço / Compra).</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>36802</t>
-  </si>
-  <si>
-    <t>Acesso Histórico Por Funcionário</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para limitar o acesso da aba "Histórico Por Funcionário" da sistema de manutenção para os mantenedores. Deixando acessível apenas para os líderes(John, Fabiano e João) , supervisor (Robmar) e a mim e o Guilherme Ferreira do setor da manutenção Usinagem. Isso seria aqui p</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>33651</t>
-  </si>
-  <si>
-    <t>Sequencia de Pre Produtivo</t>
-  </si>
-  <si>
-    <t>Bom dia, Recebi hoje o e-mail em anexo, mas ele continua com o mesmo problema: os caracteres com acentuação não são mostrados. Por gentileza verificar. Obrigada! De: Suporte Altona &gt; Enviada em: quinta-feira, 14 de agosto de 2025 08:39 Para: Laura Herrmann Schmickler &gt;; Laura Herrmann Schmickler &gt; A</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>21/08/2025</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>36689</t>
-  </si>
-  <si>
-    <t>Sistema de chamado - WMS III</t>
-  </si>
-  <si>
-    <t>Boa tarde Segue abaixo melhoria: Permitir a confirmação de coleta e entrega utilizando a tecla Enter, evitando etapas desnecessárias.</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Nova Carga de clientes.</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>36050</t>
-  </si>
-  <si>
-    <t>REGISTRO LOG DE ALTERAÇÃO DA OTF</t>
-  </si>
-  <si>
-    <t>Bom dia, Poderiam verificar pra alteração do campo abaixo ficar salvo no log de alterações: Att,</t>
-  </si>
-  <si>
-    <t>Andrew Ariel Dias</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
-    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
-  </si>
-  <si>
-    <t>36338</t>
-  </si>
-  <si>
-    <t>Listagem de CPCs do cliente Minera San Cristóbal com a margem de Contribuição (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde Maciel, Gentileza enviar uma lista das CPCs feitas para o cliente Minera San Cristóbal (código 21189), referente aos anos de 2024 e 2025 com suas respectivas margens de contribuição. Precisamos com urgência desse relatório para solicitação da diretoria comercial. Att.</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>35642</t>
-  </si>
-  <si>
-    <t>Rateio - Tempo Padrão de Modelos - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Srs., Estamos, mais uma vez, enfrentando problemas nos rateios dos tempos dos modelos. Em diversos modelos foram identificadas inconsistências significativas, e tomamos como referência o modelo 79704074 para exemplificar a situação. Tempo que sendo reteado pelo B.I. Tempo de foi importado p</t>
-  </si>
-  <si>
-    <t>Marcos Santos Junior</t>
-  </si>
-  <si>
-    <t>09/12/2025</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>37001</t>
-  </si>
-  <si>
-    <t>Comparativo de horas paradas entre SMI e MES - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>36262</t>
-  </si>
-  <si>
-    <t>Melhoria | Vinculo de Atraso na Invoice</t>
-  </si>
-  <si>
-    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>15/04/2026</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>35409</t>
-  </si>
-  <si>
-    <t>PAINEL DOS MANIPULADORES</t>
-  </si>
-  <si>
-    <t>Bom dia, Os operadores de manipuladores apontam porcentagens de peças executadas. Precisamos dessa informação de fácil acesso no painel de operações, igual ao dos jatos, que aparece no detalhamento do apontamento.</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>36482</t>
-  </si>
-  <si>
-    <t>Estorno para inventário</t>
-  </si>
-  <si>
-    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
-    <t>36287</t>
-  </si>
-  <si>
-    <t>RATPP MOVIMENTAÇÃO DO 516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Favor criar uma pergunta na movimentação do setor 516 somente para os fluxos 100, 101, 102, 103, 113, 114, 115 e 116. "HÁ NECESSIDADE DE RATPP?" com a possibilidade de resposta "SIM" ou "NÃO". Em caso de resposta "SIM", abrir saldo para o setor 567 somente após a movimentação dos setores </t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>27/01/2026</t>
-  </si>
-  <si>
-    <t>36997</t>
-  </si>
-  <si>
-    <t>% linhas mesa redonda</t>
-  </si>
-  <si>
-    <t>Bom dia, Atualização para o chamado 36157, para melhor assertividade e confiança no apontamento de %. Seria ideal ser obrigatório a escolha de peça finalizada ou não após clicar em finalizar apontamento se SIM (finalizada 100%) se NÃO (aprece a lista para indicar a % trabalhada na peça) Luiz já cien</t>
-  </si>
-  <si>
-    <t>36730</t>
-  </si>
-  <si>
-    <t>Arvore de Ativos no sistema SMI</t>
-  </si>
-  <si>
-    <t>Olá, Necessitamos que seja incluído a arvore de ativos no sistema de manutenção de forma massiva. Temos documentos em excel com as informações necessárias para a inclusão. Att,</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Rocha Junior</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>Procedimento que envie lotes de produtos cadastrados.</t>
-  </si>
-  <si>
-    <t>36685</t>
-  </si>
-  <si>
-    <t>Apontamento Tablet - Sistemas Altona</t>
-  </si>
-  <si>
-    <t>Boa tarde, referente ao sistema de apontamento dos tablets, está ocorrendo de não aparecer as operações quando transporto os dados do apontamento feito no tablet para o Excel. Isso vem acontecendo desde que as novas operações foram adicionadas, Conseguiriam fazer esse ajuste ?</t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>35353</t>
-  </si>
-  <si>
-    <t>Criação do IROG do Tratamento Térmico - Reunião para definir o que precisa ser feito</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Precisamos que seja criado uma aba para visualização do IROG do Tratamento Térmico. Incluir o ícone nessa aba: Link do apontamento do Tratamento Térmico: https://mes.altona.com.br/KB_EAA_TOTONETFrameworkOracle/wtt000.aspx Lançar os dados que estão sendo gerados nesse apontamento para a</t>
-  </si>
-  <si>
-    <t>19/11/2025</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>36484</t>
-  </si>
-  <si>
-    <t>Melhoria da Tela de Tickets - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia Maciel, Conforme falamos, precisamos melhorar a tela para a seleção das sequencias nos tickets, para reduzir o tempo de emissão das etiquetas. Alterando as telas abaixo, para que possamos abrir uma única vez a tela e selecionar a sequência e o ticket a ser incluído, passando para o próximo a</t>
-  </si>
-  <si>
-    <t>Vanessa Karsten</t>
-  </si>
-  <si>
-    <t>36075</t>
-  </si>
-  <si>
-    <t>Apontamento de solda</t>
-  </si>
-  <si>
-    <t>Bom dia. @Felipe, conforme conversamos; Necessário acrescentar informações de dados no app "solda conferencia consumo" Acrescentar coluna com "local de trabalho" de cada soldador, para distinção entre USE e KOMATSU. Hoje, ambos setores são denominados USE. Exemplo: Formatação das colunas I e J incor</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>15/01/2026</t>
-  </si>
-  <si>
-    <t>36977</t>
-  </si>
-  <si>
-    <t>VALOR DO FRETE NA BASE DE CALCULO DO ICMS</t>
-  </si>
-  <si>
-    <t>Boa tarde @sistemas@ti-altona.movidesk.com; Espero que esteja bem! Poderia por gentileza colocar no sistema de faturamento um lugar para adicionarmos o valor do frete na base de c?lculo do ICMS: Atenciosamente!</t>
-  </si>
-  <si>
-    <t>Nicolas de Souza</t>
-  </si>
-  <si>
-    <t>35500</t>
-  </si>
-  <si>
-    <t>indicador de aderência</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor abrir chamado para a situação a seguir: Criar indicador de aderência de programação no sistema de manutenção Atenciosamente...</t>
-  </si>
-  <si>
-    <t>Davi Jeronimo Andrade</t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>Incluir no cadastro de proposta a chamada do link (item 4.3)</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>36253</t>
-  </si>
-  <si>
-    <t>SISTEMA MAPEAMENTO DIGITAL</t>
-  </si>
-  <si>
-    <t>Boa tarde, Apenas para registro, Luiz conforme conversamos por gentileza verificar as questões abaixo, · Fotos que estão ficando preto e branco, · Se possível, quando finalizado o mapeamento na hora de visualizar ou imprimir ter duas opções. Opção 1 imprimir / visualizar com fotos (lembrando que tem</t>
-  </si>
-  <si>
-    <t>Danilo da Silva Pereira</t>
-  </si>
-  <si>
-    <t>33980</t>
-  </si>
-  <si>
-    <t>Dúvida</t>
-  </si>
-  <si>
-    <t>Qlik - Store e QVD do Comparativo de Carteira e Estoque - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Felipe, Gerar um QVD e Store dos arquivos da pasta F:\01-COMPARATIVO_CARTEIRA_DEPOSITO (as 03 abas). Cada arquivo deve ser amarrado pela "data de geração" dele.</t>
-  </si>
-  <si>
-    <t>08/09/2025</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>36418</t>
-  </si>
-  <si>
-    <t>Geração de dados Excel - Corte pó de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor inserir na geração dos dados de improdutividade o lado que apontou, estamos com dificuldade em saber qual é o lado que apontou. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>03/02/2026</t>
-  </si>
-  <si>
-    <t>36800</t>
-  </si>
-  <si>
-    <t>Análise Tempo médio entre falhas(MTBF)</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para analisar o tempo médio entre falhas(MTBF) pelos dados do sistema de produção, o MESS, e gere um dashboard no QlikSense na aba de indicadores.</t>
-  </si>
-  <si>
-    <t>36012</t>
-  </si>
-  <si>
-    <t>Apontamentos de Horas Acabamento</t>
-  </si>
-  <si>
-    <t>Luiz, boa tarde! Ocultar / excluir apontamentos de teste que estão aparecendo em base oficial. Sequência Modelo Cliente Unidade Negócio Liga QTDE Peso Peça Origem Apontamento Hora Início Hora Final Horas Sequência CD Operação Descrição Operação 012LR 79554315 STARA S.A. INDÚSTRIA E IMPLEMENTOS AGRÍC</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>12/01/2026</t>
-  </si>
-  <si>
-    <t>36244</t>
-  </si>
-  <si>
-    <t>Falha Sistema de Indicadores GIQ</t>
-  </si>
-  <si>
-    <t>Bom dia, pessoal! Quando teremos atualização referente a esse chamado? At.te, De: Helena Mariana Segalla Enviada em: sexta-feira, 9 de janeiro de 2026 16:47 Para: 'sistemas@ti-altona.movidesk.com' Cc: Edson João Hammermeister ; Sandro Schram Assunto: Falha Sistema de Indicadores GIQ Olá, No ano pass</t>
-  </si>
-  <si>
-    <t>Helena Mariana Segalla</t>
-  </si>
-  <si>
-    <t>37091</t>
-  </si>
-  <si>
-    <t>Aba de defeitos</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para fazer uma revisão na aba de defeitos, se possível eliminar defeitos duplicados. E ampliar a busca, por exemplo, quando digitado "BKW" só aparece a busca se ele estiver no início da frase. O ideal seria fazer uma busca mais complexa permitindo aparecer as outras opçõ</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>36756</t>
-  </si>
-  <si>
-    <t>Recusa - Altona Engenharia - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde, Devido ao novo sistema da Altona Engenharia, estamos encontrando grande dificuldade para dar entrada nas notas, pois o código do produto está vindo mesmo para todos os produtos. Em conversa com o Edson Zeferino, ele nos informou que essa informação vem diretamente do sistema e que o fatur</t>
-  </si>
-  <si>
-    <t>Talita Rodrigues Sena</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>35378</t>
-  </si>
-  <si>
-    <t>Qliksense - Aplicação Refugo</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria que fosse inserido o motivo do refugo na quarta aba, na tabela abaixo: Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Raiana Correa</t>
-  </si>
-  <si>
-    <t>21/11/2025</t>
-  </si>
-  <si>
-    <t>36393</t>
-  </si>
-  <si>
-    <t>PROCEDIMENTOS NÃO ESTÃO SENDO ANEXADOS NA ANÁLISE CRÍTICA</t>
-  </si>
-  <si>
-    <t>Bom dia! Estamos com uma situação ao preencher o formulário da análise crítica: ao tentar anexar um documento, especificamente o "PROTOCOLO DIMENSIONAL", o anexo é inserido, porém ao tentar visualizá-lo, aparece a mensagem dizendo que não é possível visualizar o arquivo. Desta forma, o anexo vai par</t>
-  </si>
-  <si>
-    <t>Rodrigo Pedroso Vargas</t>
-  </si>
-  <si>
-    <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>36797</t>
-  </si>
-  <si>
-    <t>leitura entre o WMS / ERP</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel. Precisamos desenvolver um método de leitura entre o WMS e o ERP para comparação automática de saldos. A ideia é que o sistema consiga puxar o saldo físico do ERP e confrontar com o saldo de cada modelo registrado no WMS, conforme o print anexado. Qual é a intenção desse processo? Cr</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>35097</t>
-  </si>
-  <si>
-    <t>Mapeamento Digital - Ajuste no salvamento</t>
-  </si>
-  <si>
-    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
-  </si>
-  <si>
-    <t>35367</t>
-  </si>
-  <si>
-    <t>Indicadores MTTR e MDT - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>35904</t>
-  </si>
-  <si>
-    <t>Melhoria no Sistema do Tratamento Térmico - Cargas ja executadas - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor acrescentar um botão para visualizar as cargas que já foram finalizadas no forno, junto ao lado do apontamento de parada. Essa função também temos disponível no sistema antigo do tratamento térmico. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>07/01/2026</t>
-  </si>
-  <si>
-    <t>36833</t>
-  </si>
-  <si>
-    <t>Incluir campo - Retrabalho</t>
-  </si>
-  <si>
-    <t>Bom dia Segue abaixo tela para inclusão de campo:</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>37009</t>
-  </si>
-  <si>
-    <t>Relatório estoque fornecedor (Binaar/Fiedler)</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicito a criação de um novo campo no ERP, no módulo de Materiais ou Compras, para possibilitar a geração de um relatório referente ao saldo estoque fornecedor. Em anexo, encaminho um modelo para referência.</t>
-  </si>
-  <si>
-    <t>36177</t>
-  </si>
-  <si>
-    <t>Melhorias apontamento eletrônico: Manipuladores</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos, o apontamento dos Manipuladores só precisa de mais duas coisas para tirar o papel de vez. Preciso que seja feito as seguintes alterações: - Inserir a porcentagem feita da peça no painel de produção; - Tornar as informações das paradas exclusivas do painel de paradas, trocar as aba</t>
-  </si>
-  <si>
-    <t>Maria Eduarda Santos</t>
-  </si>
-  <si>
-    <t>21/01/2026</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>33489</t>
-  </si>
-  <si>
-    <t>Implementação sistema retrabalho Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
-    <t>36340</t>
-  </si>
-  <si>
-    <t>Cadastro de e-mails - Sistemas Altona</t>
-  </si>
-  <si>
-    <t>Boa tarde pessoal, Estamos desenvolvendo o sistema Gestão de ações juntamente com o TI, e surgiu um novo problema. Utilizamos o cadastro de usuários dos sistemas Altona para encontrar e enviar e-mail automáticos de cobrança. Porém nem todos os usuários estão com esse e-mail cadastrado (o meu por exe</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>36780</t>
-  </si>
-  <si>
-    <t>Acessos anônimos</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos bloquear os acessos anônimos no sistema, mesmo que para consulta. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>36009</t>
-  </si>
-  <si>
-    <t>CONTROLE DE PROCEDIMENTOS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar novos controles para a coluna "Proced. OK" na tela WCPP22PR: Criar botão nesta mesma tela com funcionalidade similar ao botão "Pendência AC": Para tanto, ao cadastrar-se a necessidade de procedimento em um determinado setor de AC na tela WACVO0501, gerar registro de finalizaçã</t>
-  </si>
-  <si>
-    <t>Oportunidade - envio do tipo da moeda estrangeira e valor</t>
-  </si>
-  <si>
-    <t>35555</t>
-  </si>
-  <si>
-    <t>Painel Desmoldagem USE</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito algumas alterações no painel de desmoldagem USE: * Tela fica piscando, acredito que esteja atualizando a todo segundo, por favor alterar para atualizar a cada 2 minutos. (Vídeo 1) * Criar um campo de "Endereço" (Figura 1), neste campo será informado o local em que a caixa está de</t>
-  </si>
-  <si>
-    <t>Lucas da Silva Machado</t>
-  </si>
-  <si>
-    <t>03/12/2025</t>
-  </si>
-  <si>
-    <t>35999</t>
-  </si>
-  <si>
-    <t>Divergência no Relatório Funil Vendas 80%</t>
-  </si>
-  <si>
-    <t>Boa tarde Edson, Feliz Ano Novo!!! Conforme verificado, o processo 94/24 foi incluído no indicador de 80% em 09/01/2026, por volta das 14h30, conforme evidenciado no print abaixo. No entanto, ao gerar o relatório "Funil Vendas 80%", o processo não está sendo apresentado. Aparentemente, o relatório s</t>
-  </si>
-  <si>
-    <t>36626</t>
-  </si>
-  <si>
-    <t>Incremento ao BI "Peso por área" - Regras de Negócio</t>
-  </si>
-  <si>
-    <t>Bom dia, Felipe. Conforme falamos por ligação, preciso que seja realizado um incremento no BI de "Peso por área" para que seja possível visualizarmos o peso histórico filtrado por setor, e não apenas por grupo de etapa que é o caso atual. Anexo uma imagem do estado atual, neste gráfico eu gostaria s</t>
-  </si>
-  <si>
-    <t>12/02/2026</t>
-  </si>
-  <si>
-    <t>36219</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
-  </si>
-  <si>
-    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>36121</t>
-  </si>
-  <si>
-    <t>Relatório de log e filtros de métodos de preventiva</t>
-  </si>
-  <si>
-    <t>Bom dia, Conversado pessoalmente. Att,</t>
-  </si>
-  <si>
-    <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>27802</t>
-  </si>
-  <si>
-    <t>Correções no chamado 26721 - Controle na geração de Sequencias</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio, Conforme falamos pelo Teams o relatório criado para controle na geração de sequencias, que estamos avaliando continua apresentando desvios. Precisamos entender o que vem ocasionando estes desvios, o plano de ação junto da GIQ continua em aberto até conseguirmos implantar este chama</t>
-  </si>
-  <si>
-    <t>Gilsimar Carls</t>
-  </si>
-  <si>
-    <t>09/09/2024</t>
-  </si>
-  <si>
-    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
-  </si>
-  <si>
-    <t>36320</t>
-  </si>
-  <si>
-    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
-  </si>
-  <si>
-    <t>34986</t>
-  </si>
-  <si>
-    <t>Registro de inspeção</t>
-  </si>
-  <si>
-    <t>Bom dia! Favor verificar o setor 7997- reteste USE, pois quando é feita a movimentação o mesmo está puxando o registro de Partícula Magnética onde o mesmo deve registrar somente " Reteste " pois a sequência abaixo é uma peça de aço inoxidável e é realizado somente o ensaio de Liquido penetrante. Obr</t>
-  </si>
-  <si>
-    <t>Mauro Morais</t>
-  </si>
-  <si>
-    <t>30/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>36906</t>
-  </si>
-  <si>
-    <t>Melhorias no sistema de coleta de assinatura das declarações de recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde! Gostaria de solicitar algumas melhorias no sistema de coleta de assinatura, conforme descrito abaixo: 1. Exibição da lista de materiais após a assinaturaApós o colaborador realizar a assinatura na tela de visualização, é necessário que o sistema também apresente a lista de materiais que f</t>
-  </si>
-  <si>
-    <t>26/02/2026</t>
-  </si>
-  <si>
-    <t>36937</t>
-  </si>
-  <si>
-    <t>opção de consulta quantidade mapeamentos realizados por turno</t>
-  </si>
-  <si>
-    <t>Boa tarde Luiz Por gentileza poderia nos passar um relatório de mapeamento realizados por turno, 1°turno 5:00 até 13:30 e 2°turno das 1:30 até 22:00 Se possível já deixar essa opção no sistema seria interessante para facilitarmos a consulta. Desde já agradeço Atenciosamente.</t>
-  </si>
-  <si>
-    <t>27/02/2026</t>
-  </si>
-  <si>
-    <t>36737</t>
-  </si>
-  <si>
-    <t>Ajustes no Checklist de EPI's - MPO Eletrônico</t>
-  </si>
-  <si>
-    <t>Boa tarde! No checklist de EPI's do MPO Eletrônico das máquinas DALCA, LIANCO, DELTRACTOR e CLANSMAN, assim como da Ferramentaria UPR, solicito os seguintes ajustes: 1. Na pergunta referente ao capacete, atualmente consta "Capacete Laranja". Preciso que fique somente "Capacete". 1. Adicionar uma opç</t>
-  </si>
-  <si>
-    <t>Danilo dos Santos Cavalcanti</t>
-  </si>
-  <si>
-    <t>36999</t>
-  </si>
-  <si>
-    <t>Desenvolver alerta de tempo excedido com "alarme" na tela das linhas Fast Loop e Carrossel</t>
-  </si>
-  <si>
-    <t>Prezados, Favor desenvolver alerta de tempo excedido com "alarme" na tela das linhas Fast Loop e Carrossel. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>36524</t>
-  </si>
-  <si>
-    <t>CONSULTA DE SETORES EM ABERTO DE PRÉ-PRODUTIVO</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor listar todos os setores em aberto ou que ainda não receberam saldo nas sequências em aberto no sistema PCP na tela abaixo WCPP22CP. At.te</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de proposta / item</t>
-  </si>
-  <si>
-    <t>36358</t>
-  </si>
-  <si>
-    <t>Opção botão para exclusão</t>
-  </si>
-  <si>
-    <t>Bom dia, Incluir a funcionalidade de exclusão de O.M. para situações em que não exista solicitação em estoque, como ocorre com embalagens em geral. At.te</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>32996</t>
-  </si>
-  <si>
-    <t>Implementação do Checklist no sistema de Tratamento Térmico - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
-  </si>
-  <si>
-    <t>18/07/2025</t>
-  </si>
-  <si>
-    <t>35520</t>
-  </si>
-  <si>
-    <t>Aplicativo Tratamento Térmico - Bloco de Provas - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>Nova Carga de produtos.</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>36312</t>
-  </si>
-  <si>
-    <t>Nova funcionalidade na declaração de recebimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde! Identificamos a necessidade de incluir uma nova modalidade na tela de Declaração de Recebimento. Atualmente, o sistema disponibiliza apenas as seguintes opções: Ordem de CompraConsignadoRetorno de ConsertoNo entanto, alguns documentos fiscais recebidos não se enquadram nessas categorias. </t>
-  </si>
-  <si>
-    <t>28/01/2026</t>
-  </si>
-  <si>
-    <t>35738</t>
-  </si>
-  <si>
-    <t>Melhoria apontamento de corte de canais - APONTAMENTO EM LOTE</t>
-  </si>
-  <si>
-    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
-  </si>
-  <si>
-    <t>16/12/2025</t>
-  </si>
-  <si>
-    <t>36489</t>
-  </si>
-  <si>
-    <t>Trava no sistema de pré-lista da manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia! Atualmente existe uma trava no sistema de pré-lista que impede a unificação, em uma mesma pré-lista, de itens do almoxarifado com itens químicos. No entanto, o pessoal da manutenção ainda consegue realizar essa unificação. Solicitamos que a mesma trava seja aplicada também para as solicitaç</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - cliente.</t>
-  </si>
-  <si>
-    <t>36306</t>
-  </si>
-  <si>
-    <t>Controle Desmoldagem</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor avaliar a possibilidade de termos duas informações extraídas do sistema, uma delas seria o tempo de desmoldagem de cada sequência, essa informação existe na OTF. E a outra seria a data de movimentação que ocorreu a desmoldagem. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Jackson Souza</t>
-  </si>
-  <si>
-    <t>36310</t>
-  </si>
-  <si>
-    <t>Incluir o CC. 60.300 dentro de Compras e em Consequência dentro da Gerencia Supply</t>
-  </si>
-  <si>
-    <t>Incluir o CC. 60.300 dentro de Compras e em Consequencia dentro da Gerencia Supply</t>
-  </si>
-  <si>
-    <t>Clovis Stein</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>36165</t>
-  </si>
-  <si>
-    <t>Incluir Coluna Fases no Sistema de Investimentos</t>
-  </si>
-  <si>
-    <t>Bom dia Edson, Consegues incluir no fluxo de caixa analitico uma coluna com o nome da fase do projeto. Na proxima semana temos reunião e preciamos desta informação até dia 26/01... Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Rafael Pereira</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento</t>
-  </si>
-  <si>
-    <t>36348</t>
-  </si>
-  <si>
-    <t>Inclusão de parâmetro de exportação de notas</t>
-  </si>
-  <si>
-    <t>Boa tarde! Peço que na hora de exportar as notas para o sistema do Benner, seja adicionado mais um parâmetro para os produtos, conforme demonstrado abaixo: Estou solicitando essa inclusão pois agora temos 3 empresas dentro do Benner, e se não colocar como parâmetro a empresa, o sistema tenta puxar o</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - produto.</t>
-  </si>
-  <si>
-    <t>36352</t>
-  </si>
-  <si>
-    <t>Atualização de mínimos e máximos</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor atualizar as quantidade de estoque min e max dos itens da planilha. Att De: Rafael da Cruz Enviada em: domingo, 11 de janeiro de 2026 19:08 Para: João Carlos Fagundes Filho ; Gustavo Henrique Keunecke ; Alan Jonis da Silva Assunto: ENC: Atualização de mínimos e máximos Boa tarde Obr</t>
-  </si>
-  <si>
-    <t>Alan Jonis da Silva</t>
-  </si>
-  <si>
-    <t>Nova carga de oportunidades.</t>
-  </si>
-  <si>
-    <t>36321</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação – Notificação no Sistema de Assinatura Digital</t>
-  </si>
-  <si>
-    <t>Bom dia! Solicitamos a implementação de uma nova funcionalidade no sistema de coleta de assinatura digital das declarações de recebimento.A proposta consiste nas seguintes opções:1. Que, após o cadastramento da declaração de recebimento, seja disparado automaticamente um e‑mail ao requisitante, info</t>
-  </si>
-  <si>
-    <t>36196</t>
-  </si>
-  <si>
-    <t>Melhoria - Incluir Dt de Entrega e Referência de Atraso</t>
-  </si>
-  <si>
-    <t>Bom dia, Incluir na tela de Lançamento de Conhecimento de Frete 02 campos: * Após dada de Vencimento incluir data de entrega (obrigatória para o cfop da NF 5101 e 6101). Após o lançamento da NFm caso for desses CFOP, não permitir sair sem preencher, e notificar a pendencia. * Incluir campo "Frete De</t>
-  </si>
-  <si>
-    <t>27561</t>
-  </si>
-  <si>
-    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG (copy)</t>
-  </si>
-  <si>
-    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
-  </si>
-  <si>
-    <t>Guilherme Mendes</t>
-  </si>
-  <si>
-    <t>22/08/2024</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de oportunidades / proposta / item</t>
-  </si>
-  <si>
-    <t>35128</t>
-  </si>
-  <si>
-    <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Dando continuidade ao processo de melhoria nas conferências do estoque peço que insiras no relatório abaixo: duas colunas conforme descrição abaixo e planilha anexa: 1) Finalidade (MP/C) - esse parâmetro servirá para conferir se um produto está classificado corretamente e consequent</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>14/03/2026</t>
-  </si>
-  <si>
-    <t>37054</t>
-  </si>
-  <si>
-    <t>BLOQUEIO DE SETORES NO APONTAMENTO ELETRONICO - Komatsu REB VI - VII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, No apontamento eletrônico existe a aba de preenchimento ( setor ), necessitamos que quando não for preenchida o próprio sistema bloqueia o apontamento, não deixando apontar. Temos essa opção no número da cabine, se o operador não preencher a cabine o apontamento é bloqueado, Esta opção vai </t>
-  </si>
-  <si>
-    <t>Otavio Zimmermann Neto</t>
-  </si>
-  <si>
-    <t>36194</t>
-  </si>
-  <si>
-    <t>CNPJ Alfanumérico - Instrução Normativa 2.229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De: Alexandro Fernandes Correa Enviada em: terça-feira, 20 de janeiro de 2026 07:29 Para: José Carlos Emygdio ; Rubia Maiara Raasch Mota Cc: Edson João Hammermeister Assunto: ENC: [Comunicado] CNPJ Alfanumérico - Instrução Normativa 2.229 Prioridade: Alta Bom dia Para atentarmos aos nossos sistemas </t>
-  </si>
-  <si>
-    <t>36716</t>
-  </si>
-  <si>
-    <t>informação de conta bancária no debit memo</t>
-  </si>
-  <si>
-    <t>Bom dia Algumas vezes a Alstom já me questionou sobre dados bancários nos debit memos enviados, porque simplesmente não tem. No credit memo talvez não seja necessário, mas teria que ter essa informação nos debit memos, para evitar atrasos em pagamentos. Fica a sugestão. Grata</t>
-  </si>
-  <si>
-    <t>Tatiana Alves</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia! Gostaria de criar um campo no ERP para cadastro de quantidade de peças por transferência (lote de transferência) Ex: Tipo de equipamento e Quantidade 1. Caixas de ferro: XX peças do modelo YYYYYY 2. Racks Stara: XX peças do modelo AAAAAA 3. Pallets: XX peças do modelo BBBBB Quem terá acesso</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>36218</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
-  </si>
-  <si>
-    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
-    <t>Procedimento que envia lotes de oportunidade cadastradas</t>
-  </si>
-  <si>
-    <t>36417</t>
-  </si>
-  <si>
-    <t>Chamado de Manilha</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme conversa feita com o Flavio, precisamos entender a estrutura de cálculo para o sistema de MRP de manilha. Compras - Manutenção - MRP manilha. Att</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC - Adicionar ao SIGA e ajustar visual dos botões</t>
-  </si>
-  <si>
-    <t>37133</t>
-  </si>
-  <si>
-    <t>Quebra de lote para criação de pendência</t>
-  </si>
-  <si>
-    <t>boa tarde, Conforme conversado na reunião de hoje (09/03), favor liberar quebra de lote para setor da usinagem. Hoje, não há possibilidade de criar pendência sem ter que movimentar todo o lote. É importante que tenha essa possibilidade para melhorar nosso rastreio e aberturas de retrabalhos corretam</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>35753</t>
-  </si>
-  <si>
-    <t>BUG SISTEMA MAPEAMENTO DIGITAL</t>
-  </si>
-  <si>
-    <t>Boa tarde!! Em diversas situações já nos deparamos com este bug que ao iniciar um novo mapeamento, pegamos as medidas da peça pelo tablete e concluímos o mapeamento para finalizar o restante das informações na cabine, mas ao chegar na cabine e tentar abrir o mapeamento pelo Chrome (Windows) não cons</t>
-  </si>
-  <si>
-    <t>Gian Lucas Corrente</t>
-  </si>
-  <si>
-    <t>36760</t>
-  </si>
-  <si>
-    <t>B.I. Acabamento Komatsu</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Para o rateio do tempo padrão nas operações do IROG Acabamento, desconsiderar o critério da "Flag Peça Finalizada". Qualquer dúvida, estou à disposição! Atenciosamente,</t>
-  </si>
-  <si>
-    <t>36213</t>
-  </si>
-  <si>
-    <t>Alteração no sistema de manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
-  </si>
-  <si>
-    <t>36761</t>
-  </si>
-  <si>
-    <t>CONTROLE DE PRAZOS PROCEDIMENTOS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor agregar este ticket ao ticket 36009. Favor criar os seguintes pontos no sistema pré-produtivo: * Na rela TANCR011 criar um campo de data para que seja incluído a data de fechamento do item. * Na tela TACVO05 incluir campo para cadastro do prazo de procedimento (em dias): * Na tela W</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de item.</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que as etapas de Saida Deposito do WMS possam ser revertidas e editadas após o processo "finalizado". * Uma vez realizado o carregamento, que seja possível , voltar e excluir NF / itens. Sugestão: selecionar os romaneios (já vinculados a NF) e excluir, voltando os Romaneios a St</t>
-  </si>
-  <si>
-    <t>22/05/2025</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>36750</t>
-  </si>
-  <si>
-    <t>ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL - Ajustes no editor de mapeamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">________________________________ De: Gian Lucas Corrente Enviado: sexta-feira, 6 de fevereiro de 2026 18:32 Para: Danilo da Silva Pereira ; Luiz Gustavo de Salles Pinho ; Sergio Schmidt Cc: Barbara Braatz Vetter Assunto: RES: ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL NA TELA “INFORMAÇÕES DO MAPEAMENTO” </t>
-  </si>
-  <si>
-    <t>Luiz Gustavo de Salles Pinho</t>
-  </si>
-  <si>
-    <t>36366</t>
-  </si>
-  <si>
-    <t>VISUALIZAÇÃO DE PORCENTAGEM E TEMPO DISPONIVEL APONTAMENTO ELETRONICO USE (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, Para melhorar visualização dos operadores, precisamos de um campo que mostre o percentual disponível e o tempo ainda disponível da peça referente ao tempo padrão. Tela para mostrar os dados solicitados após indicar sequência, caso ultrapasse o tempo disponível (padrão) retornar 0 hrs. Qua</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>31701</t>
-  </si>
-  <si>
-    <t>Extrações para IA SENAI</t>
-  </si>
-  <si>
-    <t>36220</t>
-  </si>
-  <si>
-    <t>INFORMAÇÕES SOBRE MATERIAL DO MODELO EM FTF'S DE CONJUNTO</t>
-  </si>
-  <si>
-    <t>35527</t>
-  </si>
-  <si>
-    <t>Orçamento 2025 - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Marcio Silva</t>
-  </si>
-  <si>
-    <t>36764</t>
-  </si>
-  <si>
-    <t>Falha ao salvar mapeamento</t>
-  </si>
-  <si>
-    <t>Testar e identificar possíveis falhas ao salvar o mapeamento digital, * Adicionar medidas para quando ocorrer qualquer erro no JS avisar ao usuário * Adicionar gatilhos para quando identificar que o json final está com o valor inicial forcar o js a gerar os dados</t>
-  </si>
-  <si>
-    <t>37033</t>
-  </si>
-  <si>
-    <t>WMS - tela resumo de atividade</t>
-  </si>
-  <si>
-    <t>Boa tarde! No WMS gostaria de crie uma tela resumo de atividade por área de acionamento: 1. Lista das origens 2. Ativo | Não ativo 3. Data e Hora do último Acionamento Obrigado! Obter o Outlook para iOS</t>
-  </si>
-  <si>
-    <t>36719</t>
-  </si>
-  <si>
-    <t>ADIÇÃO DE CAIXA DE PESQUISA</t>
-  </si>
-  <si>
-    <t>Bom dia, tudo bem? Solicito a inclusão de uma caixa de pesquisa por nome do fornecedor para se tornar mais fácil a localização das pesagens assim como já existe a caixa de pesquisa por placa. Att.</t>
-  </si>
-  <si>
-    <t>Manuelle Teixeira Sampaio</t>
-  </si>
-  <si>
-    <t>33048</t>
-  </si>
-  <si>
-    <t>Custos FTF</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
-  </si>
-  <si>
-    <t>22/07/2025</t>
-  </si>
-  <si>
-    <t>34952</t>
-  </si>
-  <si>
-    <t>Criação Relatório BI ProfMix</t>
-  </si>
-  <si>
-    <t>Incluir no cadastro de oportunidades a chamada do link (item 3.3)</t>
-  </si>
-  <si>
-    <t>Criar procedimento que envie lotes de Oportunidades</t>
-  </si>
-  <si>
-    <t>37063</t>
-  </si>
-  <si>
-    <t>Desconto de Paradas do Tempo Produtivo</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme conversado em chamada com o Felipe, os tempos produtivos apontados para os Jatos, não estão descontando os tempos de paradas apontadas. Nesse caso acima (teste), foi apontado 5min produtivos, porem tivemos 1min de parada que não descontou do tempo produtivo. Outro chamado em andame</t>
-  </si>
-  <si>
-    <t>37019</t>
-  </si>
-  <si>
-    <t>Baixa Automática Material de Estoque por Nota Fiscal de Venda Sucata</t>
-  </si>
-  <si>
-    <t>Bom dia a todos! Sandro, Desenvolver a baixa de itens (materiais) que tenham controle de estoque automaticamente. ________________________________ De: Sandro Schram Enviadas: Quarta-feira, 04 de Março de 2026 08:40 Para: Paulo Giovani da Cruz ; Marcelo Americo Cc: Marcio Silva ; Cezar Gomes de Olive</t>
-  </si>
-  <si>
-    <t>35067</t>
-  </si>
-  <si>
-    <t>Erro IROG acabamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
-  </si>
-  <si>
-    <t>Carlos Correia</t>
-  </si>
-  <si>
-    <t>Incluir no cadastro do item da proposta a chamada do link (item 5.3)</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>36304</t>
-  </si>
-  <si>
-    <t>Solicitação de Melhorias no Sistema de Coleta de Assinaturas</t>
-  </si>
-  <si>
-    <t>Bom dia! Precisamos implementar algumas melhorias no sistema de coleta de assinatura das declarações de recebimento. Seguem os pontos identificados: Validação de NF: Implementar uma verificação para identificar se a Nota Fiscal foi emitida contra a Altona ou se passou pela portaria, garantindo que e</t>
-  </si>
-  <si>
-    <t>B.I. Acabamento - Alimentar dados retroativos</t>
-  </si>
-  <si>
-    <t>32989</t>
-  </si>
-  <si>
-    <t>IROG Tratamento Térmico no BI - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Foi conversado que, com as informações presentes hoje no sistema (disponibilidade, performance e qualidade), pode-se iniciar a implantação do IROG no BI. Em paralelo, o time da TI irá conduzir as melhorias pontuadas. Edson informou que o BI e melhorias serão atendidos em um mesmo chamado; 1</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>34335</t>
-  </si>
-  <si>
-    <t>Tempo Padrão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
-  </si>
-  <si>
-    <t>34012</t>
-  </si>
-  <si>
-    <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estamos com uma ação vinculada ao projeto Produttare e algumas frentes de implementação de indicadores na área de Manutenção. Precisamos da ajuda do time de TI para iniciarmos com um painel de indicadores com as seguintes sugestões para implementação via Qlikview. Indicador MDT (Mean down</t>
-  </si>
-  <si>
-    <t>09/09/2025</t>
-  </si>
-  <si>
-    <t>29848</t>
-  </si>
-  <si>
-    <t>Alteração da referencia de Etiqueta para Romaneio - Validação</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>36278</t>
-  </si>
-  <si>
-    <t>Altona || Estoque Consignado Binaar</t>
-  </si>
-  <si>
-    <t>Boa tarde, Edson Precisamos devolver o estoque de consignados da Binaar até dia 30/01/2026 por uma orientação do Cleber. Peço que revejas com o Sandro a possibilidade dele focar nessa tarefa para conseguirmos cumprir com a solicitação da diretoria. Obrigado</t>
-  </si>
-  <si>
-    <t>36690</t>
-  </si>
-  <si>
-    <t>Sistema de chamado - WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde Segue abaixo melhoria: Reduzir confirmações repetitivas de "sim" durante os processos de coleta e entrega, agilizando o fluxo</t>
-  </si>
-  <si>
-    <t>36871</t>
-  </si>
-  <si>
-    <t>Inventario Filial</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos de uma tela para inventário nos itens do "Estoque Fornecedor". Em conversa com o Alex, ele comentou que deve ser nessa tela. Sandro, estamos querendo implementar uma melhoria para controle de estoque, fazer a baixa desse estoque direto com o coletor padrão do Almoxarifado. E cons</t>
-  </si>
-  <si>
-    <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>ALTERAÇÕES SISTEMA MAPEAMENTO DIGITAL - Criar nova tela para tirar fotos e ajustar a grid de visualização</t>
-  </si>
-  <si>
-    <t>36668</t>
-  </si>
-  <si>
-    <t>Sistema de chamado - WMS II</t>
-  </si>
-  <si>
-    <t>37022</t>
-  </si>
-  <si>
-    <t>sistema de apontamento da lubrificação</t>
-  </si>
-  <si>
-    <t>Bom dia, precisamos inserir no sistema de manutenção um método de apontamento para os lubrificadores onde eles consigam colocar a quantidade de lubrificantes, tipo de lubrificantes e serviço. Para poder gerarmos relatórios de consumo e custos de lubrificante gasto . Podemos marcar uma reunião para a</t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>36898</t>
-  </si>
-  <si>
-    <t>Itens em falta - Criticidade do item e relatório no Sense</t>
-  </si>
-  <si>
-    <t>Bom dia, Preciso de um relatório no qliksense com lista de todos os materiais com saldo zerado no sistema. E precisamos adicionar no cadastro do material a criticidade do item, A,B,C. quando tiver essa informação ela deve estar nesse relatório junto com as peças que estão faltando. Att</t>
-  </si>
-  <si>
-    <t>35047</t>
-  </si>
-  <si>
-    <t>Atualização de aplicações</t>
-  </si>
-  <si>
-    <t>Bom dia, Preciso que as seguintes aplicações sejam atualizadas diariamente às 09h00 da manhã e às 13h00 da tarde. Estão no fluxo de suprimentos. Att</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>36157</t>
-  </si>
-  <si>
-    <t>APONTAMENTO LINHAS UPR (acrescentar opção de apontamento de % nas linhas UPR)</t>
-  </si>
-  <si>
-    <t>Acrescentar opção de apontamento de % nas linhas UPR, disponibilizar lista de 10 em 10%. A soma não pode ultrapassar os 100%.</t>
-  </si>
-  <si>
-    <t>20/01/2026</t>
-  </si>
-  <si>
-    <t>36475</t>
-  </si>
-  <si>
-    <t>PESO DE CONJUNTO CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar uma nova regra em CPPs de tipo Normal e Componente onde o peso de conjunto seja preenchido automaticamente utilizando a fórmula abaixo: (Peso Bruto + Peso Alimentação) x Qtde Modelos P/Placa = Peso Conjunto. Hoje esse cálculo já é feito nos formulários de análise crítica dos s</t>
-  </si>
-  <si>
-    <t>36460</t>
-  </si>
-  <si>
-    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo UInventa</t>
-  </si>
-  <si>
-    <t>Sandro, dando continuidade ao chamado 35127 identifiquei dois problemas: 1) O saldo anterior + entradas - consumo está diferente do valor apresentado no inventário (imagem 1) Imagem 1 2) O saldo do inventário em excel está diferente do relatório em PDF. NO excel ainda tem uma faixa de itens a ser li</t>
-  </si>
-  <si>
-    <t>36302</t>
-  </si>
-  <si>
-    <t>Altona || OSI - Suspensão</t>
-  </si>
-  <si>
-    <t>Bom dia! O Richard encerrou o chamado 35369 e como eu cadastrei o nome incorretamente, deixei passar. Esse chamado é uma continuação do 35369.</t>
-  </si>
-  <si>
-    <t>35731</t>
-  </si>
-  <si>
-    <t>Indicadores Moldes Moldagem USE</t>
-  </si>
-  <si>
-    <t>Bom dia. Preciso criar/adaptar um aplicativo do QlikSense. Hoje há um aplicativo que mostra as movimentações por sequência de peça, porém preciso que esse indicador seja apresentado por quantidade de moldes. Para isso, há a informação do sistema da quantidade de peças por placa de moldagem, conforme</t>
-  </si>
-  <si>
-    <t>37010</t>
-  </si>
-  <si>
-    <t>Relatório em Excel no sistema de inventário de embalagens</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicito a implementação de um relatório com comparativo saldo atual X quantidade física. pode-se utilizar como referencia o relatório existente hoje no modelo de inventário do Almoxarifado.</t>
-  </si>
-  <si>
-    <t>35747</t>
-  </si>
-  <si>
-    <t>Criar novo código de operação para o QlikSense</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos. Atualmente nós apontamos os dados da máquina Lianco (setor 1531) e Dalca (setor 1530) no sistema de Apontamento de Produção, e no QlikSense mostra exatamente os dados que apontamos, e como não apontamos uma "operação" acaba que no QlikSense não aparece código de operação. Porém is</t>
-  </si>
-  <si>
-    <t>36743</t>
-  </si>
-  <si>
-    <t>Aplicação sem dados após 06/02</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor verificar a aplicação parou de gerar os dados de auditoria depois do dia 06/02/2026. Acredito que tenha vínculo com os apontamentos de máquina, o qual sofreu alteração de sistema. Grato,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>36298</t>
-  </si>
-  <si>
-    <t>APONTAMENTO LINHAS UPR (TAXA DE ATUALIZAÇÃO)</t>
-  </si>
-  <si>
-    <t>Verificada lentidão na taxa de atualização a cada etapa/clique, apontamento linha mesa redonda.</t>
-  </si>
-  <si>
-    <t>37025</t>
-  </si>
-  <si>
-    <t>Melhorias no sistema de cadastro de matérias</t>
-  </si>
-  <si>
-    <t>Bom dia, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1.Puxar as seguintes informações tipo produto; grupo; Ressuprimentos. Conforme imagem abaixo 2. Colocar um campo de data, na opção de aprovar cadastros.</t>
-  </si>
-  <si>
-    <t>35792</t>
-  </si>
-  <si>
-    <t>Criação de campos no sistema de manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
-  </si>
-  <si>
-    <t>Vitor de Oliveira da Silva</t>
-  </si>
-  <si>
-    <t>18/12/2025</t>
-  </si>
-  <si>
-    <t>36125</t>
-  </si>
-  <si>
-    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>15/10/2024</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - oportunidade.</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>20/08/2025</t>
-  </si>
-  <si>
-    <t>36142</t>
-  </si>
-  <si>
-    <t>Incluir no relatório de aciaria o saldo em estoque de terceiro</t>
-  </si>
-  <si>
-    <t>36229</t>
-  </si>
-  <si>
-    <t>Troca de campanha forno indução</t>
-  </si>
-  <si>
-    <t>Solicito troca sistemática da troca de campanha no forno indução, Sistema semelhante ao da troca de campanha de panelas Segue local e o sistema de corridas:</t>
-  </si>
-  <si>
-    <t>34225</t>
-  </si>
-  <si>
-    <t>Correções Relatório Faturamento por Sequência - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>04/06/2025</t>
-  </si>
-  <si>
-    <t>35550</t>
-  </si>
-  <si>
-    <t>Implementação de Índice de Qualidade de Manutenção</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estou formalizando a solicitação da implementação de uma sistemática de índice de qualidade para os serviços de manutenção. Dessa maneira precisamos implementar um sistema de Status "Baixado" ser a última etapa do processo interno de manutenção e assim que o Status for "Baixado" o sistema</t>
-  </si>
-  <si>
-    <t>02/12/2025</t>
-  </si>
-  <si>
-    <t>34896</t>
-  </si>
-  <si>
-    <t>Alteração de calculo do BI</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., 1ª Alteração: Precisamos alterar o cálculo da performance conforme abaixo: O Tempo Padrão deve ser considerado por sequência e operação. Caso sejam apontados a mesma operação por mais de uma vez para a mesma sequência, o Tempo Padrão deve ser rateado entre estes apontamentos, levando</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>24/10/2025</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
-  </si>
-  <si>
-    <t>36441</t>
-  </si>
-  <si>
-    <t>Qlik | Aplicação de Reconhecimento de Receita</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza fazer o vínculo de atualização da aplicação - Logistica &gt; 2 - Reconhecimento de Receita Root/QVD/EXTRACAO/NFEDESP.qvd] - Nota fiscal Root/QVD/EXTRACAO/CPC389.qvd] - Invoice Root/QVD/EXTRACAO/CTEEMIT.qvd] - Cte (Obs: o chamado 36196 possui 02 campos novos que quando feitos precisam</t>
-  </si>
-  <si>
-    <t>36706</t>
-  </si>
-  <si>
-    <t>B.I. de Horas Extras - (ACOMPANHAMENTO DGL)</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., O B.I. de Horas Extras não está trazendo a informação correta das horas dos setores. Aplicação: https://qliksense.altona.com.br/sense/app/35b883e4-7632-42f7-b87e-947c084b3368/sheet/1cf87029-9ed9-4cdb-916c-d99d96f33693/state/analysis Como exemplo as horas da Gerência da Inspeção! Hora</t>
-  </si>
-  <si>
-    <t>17/02/2026</t>
-  </si>
-  <si>
-    <t>36717</t>
-  </si>
-  <si>
-    <t>DATA LIMITE PARA BAIXA DE O.S</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de implementar uma opção no sistema de manutenção, onde possa ser limitado e/ou justificado o motivo da ordem não ter sido baixada no tempo hábil. Exemplo: Peguei uma O.S. no dia 17/02/2026, com a função habilitada e definida pelo usuário, tenho o limite de dias conforme a O.S. (em</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>36375</t>
-  </si>
-  <si>
-    <t>Controle de Periodo Firme da Programacao da Carteira</t>
-  </si>
-  <si>
-    <t>Gentileza incluir a @Caroline Schmitt e o @Gilsimar Carls no recebimento desse email -----Mensagem original----- De: ERP Altona Enviada em: sexta-feira, 30 de janeiro de 2026 06:04 Para: Taynara Frare Assunto: Controle de Periodo Firme da Programacao da Carteira Prezado usuário, segue em anexo plani</t>
-  </si>
-  <si>
-    <t>Taynara Frare</t>
-  </si>
-  <si>
-    <t>Indicador de Aderencia - Carga de dados</t>
-  </si>
-  <si>
-    <t>36301</t>
-  </si>
-  <si>
-    <t>AOD - Panelas</t>
-  </si>
-  <si>
-    <t>Sistema de Apontamento de panelas deve ser no AOD igual aos demais fornos</t>
-  </si>
-  <si>
-    <t>36487</t>
-  </si>
-  <si>
-    <t>Altona || Nota de devolução de compra sem Requisição de Estoque</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Peço tua ajuda para criar uma rotina que não permita mais que notas de devolução de compra com itens de estoque sejam emitidas sem a respectiva requisição de devolução. Sugiro que ao adicionar o produto (no processo de emissão de nota), o SNB verifique se esse item é estoque (Contas</t>
-  </si>
-  <si>
-    <t>36326</t>
-  </si>
-  <si>
-    <t>Modelos com vazamento a mais de 4 anos</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza incluir a caroline.schmitt@altona.com.br no recebimento desses e-mails. Alterar a frequência para 1x na semana (todas as segundas-feiras). -----Mensagem original----- De: Modelos com vazamento a mais de 4 anos Enviada em: quinta-feira, 29 de janeiro de 2026 05:12 Para: taynara.fra</t>
-  </si>
-  <si>
-    <t>36327</t>
-  </si>
-  <si>
-    <t>Sequencias paradas no setor</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza incluir a caroline.schmitt@altona.com.br no recebimento desses e-mails. -----Mensagem original----- De: Sequencias paradas no setor Enviada em: quinta-feira, 29 de janeiro de 2026 06:50 Para: pendencias.aciaria@ Assunto: Sequencias paradas no setor Em anexo segue lista de sequenci</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Automação da lista de presença - Detalhar escopo</t>
-  </si>
-  <si>
-    <t>36245</t>
-  </si>
-  <si>
-    <t>Carregar dados no QlikSense</t>
-  </si>
-  <si>
-    <t>Bom dia, pessoal! Quando teremos atualização referente a esse chamado? At.te, De: Helena Mariana Segalla Enviada em: sexta-feira, 9 de janeiro de 2026 09:30 Para: 'sistemas@ti-altona.movidesk.com' Cc: Edson João Hammermeister ; Richard Rene Zalasik ; Sandro Schram Assunto: ENC: Carregar dados no Qli</t>
-  </si>
-  <si>
-    <t>36705</t>
-  </si>
-  <si>
-    <t>MODIFICAÇÃO NO SISTEMA DE MANUTENÇÃO</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de adicionar uma opção no sistema de manutenção, na aba de "permissões" - Adicionar um limite de ordens em andamento, como o exemplo abaixo: (além do "Limite de Paradas Permitidas", colocar o "Limite de ordens em andamento"). Aguardo retorno,</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Valorização de modelos</t>
-  </si>
-  <si>
-    <t>31977</t>
-  </si>
-  <si>
-    <t>Alterações no registro de moldagem via APP - Validação</t>
-  </si>
-  <si>
-    <t>36453</t>
-  </si>
-  <si>
-    <t>Divergência no Relatório Funil Vendas 80% - Acompanhamento</t>
-  </si>
-  <si>
-    <t>36398</t>
-  </si>
-  <si>
-    <t>Add opção de revisão valor de frete na CPC</t>
-  </si>
-  <si>
-    <t>@Maciel, bom dia! Conforme conversamos, por gentileza adicionar uma tela para revisão de tipo de frete na CPC. Precisamos ter qual a nova opção de frete (DAP, DDP, FOB, etc.) e qual o valor da diferença. Obrigada!</t>
-  </si>
-  <si>
-    <t>36692</t>
-  </si>
-  <si>
-    <t>Sequencias de conjunto</t>
-  </si>
-  <si>
-    <t>Boa tarde, Maciel. Conforme conversamos, precisamos que as informações das sequências do conjunto sejam exibidas diretamente na tela atual do WMS. Atualmente, a consulta dessas sequências precisa ser feita por meio de outras telas, o que tem aumentado nosso tempo de análise e, consequentemente, noss</t>
-  </si>
-  <si>
-    <t>37327</t>
-  </si>
-  <si>
-    <t>Porcentagem manipuladores</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos, eu e o Douglas Garcia percebemos um erro no painel de produção dos manipuladores e na extração dos dados. A porcentagem executada está sempre aparecendo como 100%, mesmo sendo apontado porcentagens diferentes, fizemos um teste de apontamento para saber se não era erro na hora de a</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Pendencias e retrabalhos nas ordens geradas e novas</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>10/02/2025</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo.</t>
-  </si>
-  <si>
-    <t>Alterar as estruturas das tabelas de op para considerar as múltiplas modelagens, e múltiplos ambientes no sql (produção e qualidade).</t>
-  </si>
-  <si>
-    <t>Para a geração das OP’s eu considero que o melhor seria termos um plano mestre por SKU, com datas e quantidades</t>
-  </si>
-  <si>
-    <t>37151</t>
-  </si>
-  <si>
-    <t>ERRO NA SELEÇÃO DE PARADA SEM SEQUÊNCIA LINHA MESA REDONDA UPR</t>
-  </si>
-  <si>
-    <t>Bom dia, Luiz, Possível erro na seleção de parada sem sequência favor avaliar. Em anexo vídeo do apontamento da peça 590LZ que é uma peça de sequência única indicando que seria uma peça lote possível erro de cadastro da sequencia ou modelo, Qualquer dúvida a disposição;</t>
   </si>
   <si>
     <t>36605</t>
@@ -3096,7 +3057,7 @@
         <v>73</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -3105,12 +3066,12 @@
         <v>49</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -3122,28 +3083,28 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>49</v>
@@ -3154,7 +3115,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -3166,22 +3127,22 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>55</v>
@@ -3198,7 +3159,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -3210,25 +3171,25 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -3492,7 +3453,7 @@
         <v>120</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -3571,7 +3532,7 @@
         <v>39</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>22</v>
@@ -3756,7 +3717,7 @@
         <v>149</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>144</v>
@@ -3800,7 +3761,7 @@
         <v>154</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>59</v>
@@ -3814,34 +3775,34 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>55</v>
@@ -3858,22 +3819,22 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -3902,37 +3863,37 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -3958,7 +3919,7 @@
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>47</v>
@@ -3990,7 +3951,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -4002,16 +3963,16 @@
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>22</v>
@@ -4034,22 +3995,22 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>39</v>
@@ -4061,10 +4022,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -4078,28 +4039,28 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
@@ -4122,37 +4083,37 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="K34" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -4166,34 +4127,34 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -4210,37 +4171,37 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="I36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -4372,7 +4333,7 @@
         <v>142</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -4425,7 +4386,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4460,7 +4421,7 @@
         <v>217</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -4677,7 +4638,7 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>239</v>
@@ -4724,7 +4685,7 @@
         <v>244</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -4847,7 +4808,7 @@
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
@@ -4900,7 +4861,7 @@
         <v>260</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -5032,7 +4993,7 @@
         <v>136</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -5076,7 +5037,7 @@
         <v>276</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>277</v>
+        <v>168</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>144</v>
@@ -5090,37 +5051,37 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H56" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="K56" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -5134,28 +5095,28 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>22</v>
@@ -5178,34 +5139,34 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="I58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>47</v>
@@ -5222,28 +5183,28 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
@@ -5252,7 +5213,7 @@
         <v>226</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -5278,7 +5239,7 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>47</v>
@@ -5310,37 +5271,37 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H61" s="2" t="s">
+      <c r="I61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="K61" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -5354,28 +5315,28 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>225</v>
@@ -5398,34 +5359,34 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>24</v>
@@ -5442,22 +5403,22 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -5469,7 +5430,7 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>47</v>
@@ -5486,22 +5447,22 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>39</v>
@@ -5513,7 +5474,7 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>143</v>
@@ -5530,34 +5491,34 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H66" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>143</v>
@@ -5569,7 +5530,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5586,7 +5547,7 @@
         <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>47</v>
@@ -5618,22 +5579,22 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -5662,7 +5623,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -5674,25 +5635,25 @@
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -5701,27 +5662,27 @@
         <v>126</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -5733,10 +5694,10 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -5750,22 +5711,22 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E71" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -5777,7 +5738,7 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>24</v>
@@ -5794,34 +5755,34 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="F72" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="G72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="I72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>239</v>
@@ -5838,28 +5799,28 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
@@ -5882,34 +5843,34 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="G74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>239</v>
@@ -5938,7 +5899,7 @@
         <v>30</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>47</v>
@@ -5970,51 +5931,51 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>354</v>
+        <v>47</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>355</v>
+        <v>47</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -6026,10 +5987,10 @@
         <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>39</v>
@@ -6041,7 +6002,7 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>239</v>
@@ -6058,7 +6019,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -6070,10 +6031,10 @@
         <v>30</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>39</v>
@@ -6085,7 +6046,7 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>239</v>
@@ -6114,7 +6075,7 @@
         <v>30</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>47</v>
@@ -6146,7 +6107,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -6158,10 +6119,10 @@
         <v>30</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -6176,7 +6137,7 @@
         <v>234</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>59</v>
@@ -6190,7 +6151,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -6202,10 +6163,10 @@
         <v>30</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -6217,7 +6178,7 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>67</v>
@@ -6234,7 +6195,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -6246,10 +6207,10 @@
         <v>30</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -6261,7 +6222,7 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>143</v>
@@ -6278,7 +6239,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -6290,10 +6251,10 @@
         <v>30</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -6308,7 +6269,7 @@
         <v>154</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -6334,7 +6295,7 @@
         <v>30</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>47</v>
@@ -6366,7 +6327,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -6378,25 +6339,25 @@
         <v>30</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -6410,7 +6371,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -6422,25 +6383,25 @@
         <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>389</v>
+        <v>337</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -6454,7 +6415,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -6466,16 +6427,16 @@
         <v>30</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>22</v>
@@ -6484,7 +6445,7 @@
         <v>276</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>25</v>
@@ -6498,7 +6459,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -6507,42 +6468,42 @@
         <v>29</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -6554,16 +6515,16 @@
         <v>30</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>22</v>
@@ -6598,7 +6559,7 @@
         <v>30</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>47</v>
@@ -6630,7 +6591,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -6642,16 +6603,16 @@
         <v>30</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>22</v>
@@ -6686,7 +6647,7 @@
         <v>30</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>47</v>
@@ -6718,7 +6679,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -6730,10 +6691,10 @@
         <v>30</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
@@ -6748,7 +6709,7 @@
         <v>125</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>25</v>
@@ -6762,7 +6723,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -6774,10 +6735,10 @@
         <v>30</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -6789,10 +6750,10 @@
         <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
@@ -6806,7 +6767,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -6818,25 +6779,25 @@
         <v>30</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>25</v>
@@ -6862,7 +6823,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>47</v>
@@ -6894,7 +6855,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -6906,25 +6867,25 @@
         <v>30</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>25</v>
@@ -6938,7 +6899,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -6950,16 +6911,16 @@
         <v>30</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>22</v>
@@ -6982,7 +6943,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -6994,25 +6955,25 @@
         <v>30</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>25</v>
@@ -7026,7 +6987,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -7038,22 +6999,22 @@
         <v>30</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>239</v>
@@ -7070,7 +7031,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -7082,22 +7043,22 @@
         <v>30</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>47</v>
@@ -7114,7 +7075,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -7126,10 +7087,10 @@
         <v>30</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>20</v>
@@ -7141,10 +7102,10 @@
         <v>22</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>442</v>
+        <v>137</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>25</v>
@@ -7170,7 +7131,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>47</v>
@@ -7202,7 +7163,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -7214,16 +7175,16 @@
         <v>30</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>22</v>
@@ -7232,7 +7193,7 @@
         <v>217</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>25</v>
@@ -7246,7 +7207,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -7258,10 +7219,10 @@
         <v>47</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>20</v>
@@ -7290,7 +7251,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -7302,22 +7263,22 @@
         <v>30</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>143</v>
@@ -7334,7 +7295,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -7346,22 +7307,22 @@
         <v>30</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>67</v>
@@ -7378,7 +7339,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -7390,10 +7351,10 @@
         <v>30</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>39</v>
@@ -7405,7 +7366,7 @@
         <v>22</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>239</v>
@@ -7422,7 +7383,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -7434,10 +7395,10 @@
         <v>30</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>39</v>
@@ -7449,7 +7410,7 @@
         <v>22</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>143</v>
@@ -7466,7 +7427,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -7478,22 +7439,22 @@
         <v>30</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>239</v>
@@ -7522,7 +7483,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>47</v>
@@ -7554,7 +7515,7 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
@@ -7566,10 +7527,10 @@
         <v>30</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>20</v>
@@ -7581,7 +7542,7 @@
         <v>22</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>47</v>
@@ -7593,12 +7554,12 @@
         <v>92</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>15</v>
@@ -7610,22 +7571,22 @@
         <v>30</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>239</v>
@@ -7642,7 +7603,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>15</v>
@@ -7654,10 +7615,10 @@
         <v>30</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>20</v>
@@ -7669,10 +7630,10 @@
         <v>225</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>355</v>
+        <v>473</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>480</v>
+        <v>234</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>25</v>
@@ -7686,7 +7647,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>15</v>
@@ -7698,10 +7659,10 @@
         <v>47</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>39</v>
@@ -7730,7 +7691,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>15</v>
@@ -7742,10 +7703,10 @@
         <v>47</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>20</v>
@@ -7774,7 +7735,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>15</v>
@@ -7786,22 +7747,22 @@
         <v>30</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>47</v>
@@ -7818,7 +7779,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>15</v>
@@ -7830,25 +7791,25 @@
         <v>30</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>25</v>
@@ -7862,7 +7823,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>15</v>
@@ -7874,22 +7835,22 @@
         <v>30</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>47</v>
@@ -7906,7 +7867,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>15</v>
@@ -7918,25 +7879,25 @@
         <v>30</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>25</v>
@@ -7950,7 +7911,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -7962,10 +7923,10 @@
         <v>30</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>39</v>
@@ -7977,7 +7938,7 @@
         <v>22</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>47</v>
@@ -7994,7 +7955,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>15</v>
@@ -8006,10 +7967,10 @@
         <v>47</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>39</v>
@@ -8050,7 +8011,7 @@
         <v>30</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>47</v>
@@ -8094,7 +8055,7 @@
         <v>30</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>47</v>
@@ -8126,7 +8087,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>15</v>
@@ -8138,10 +8099,10 @@
         <v>30</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>39</v>
@@ -8170,7 +8131,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>15</v>
@@ -8182,10 +8143,10 @@
         <v>30</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>20</v>
@@ -8197,7 +8158,7 @@
         <v>22</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>47</v>
@@ -8214,7 +8175,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>15</v>
@@ -8226,16 +8187,16 @@
         <v>17</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>22</v>
@@ -8244,7 +8205,7 @@
         <v>46</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L127" s="2" t="s">
         <v>25</v>
@@ -8270,7 +8231,7 @@
         <v>30</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>47</v>
@@ -8302,7 +8263,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>15</v>
@@ -8314,22 +8275,22 @@
         <v>30</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>47</v>
@@ -8341,12 +8302,12 @@
         <v>92</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>15</v>
@@ -8358,10 +8319,10 @@
         <v>30</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>20</v>
@@ -8373,7 +8334,7 @@
         <v>22</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>67</v>
@@ -8402,7 +8363,7 @@
         <v>17</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>19</v>
@@ -8434,7 +8395,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>15</v>
@@ -8446,10 +8407,10 @@
         <v>30</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>39</v>
@@ -8461,7 +8422,7 @@
         <v>22</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>239</v>
@@ -8478,7 +8439,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>15</v>
@@ -8490,10 +8451,10 @@
         <v>30</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>20</v>
@@ -8505,24 +8466,24 @@
         <v>225</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="M133" s="2" t="s">
         <v>49</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>15</v>
@@ -8534,10 +8495,10 @@
         <v>30</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>39</v>
@@ -8549,7 +8510,7 @@
         <v>22</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>143</v>
@@ -8561,12 +8522,12 @@
         <v>92</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>15</v>
@@ -8578,10 +8539,10 @@
         <v>30</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>39</v>
@@ -8593,10 +8554,10 @@
         <v>22</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="L135" s="2" t="s">
         <v>25</v>
@@ -8605,12 +8566,12 @@
         <v>26</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>15</v>
@@ -8622,10 +8583,10 @@
         <v>30</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>20</v>
@@ -8637,10 +8598,10 @@
         <v>225</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>25</v>
@@ -8654,7 +8615,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>15</v>
@@ -8666,25 +8627,25 @@
         <v>30</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>268</v>
+        <v>86</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>25</v>
@@ -8698,7 +8659,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>15</v>
@@ -8710,10 +8671,10 @@
         <v>30</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>20</v>
@@ -8742,7 +8703,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>15</v>
@@ -8754,22 +8715,22 @@
         <v>30</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>555</v>
+        <v>197</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>24</v>
@@ -8786,7 +8747,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>15</v>
@@ -8798,22 +8759,22 @@
         <v>30</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>239</v>
@@ -8830,7 +8791,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>15</v>
@@ -8842,10 +8803,10 @@
         <v>47</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>20</v>
@@ -8874,7 +8835,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>15</v>
@@ -8886,22 +8847,22 @@
         <v>30</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>143</v>
@@ -8918,7 +8879,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>15</v>
@@ -8930,22 +8891,22 @@
         <v>30</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>24</v>
@@ -8962,7 +8923,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>15</v>
@@ -8971,42 +8932,42 @@
         <v>29</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>404</v>
+        <v>47</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>569</v>
+        <v>47</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>15</v>
@@ -9018,10 +8979,10 @@
         <v>30</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>39</v>
@@ -9033,10 +8994,10 @@
         <v>22</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>25</v>
@@ -9050,7 +9011,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>15</v>
@@ -9062,16 +9023,16 @@
         <v>30</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>22</v>
@@ -9094,7 +9055,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>15</v>
@@ -9106,16 +9067,16 @@
         <v>30</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>22</v>
@@ -9138,7 +9099,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>15</v>
@@ -9150,22 +9111,22 @@
         <v>30</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>24</v>
@@ -9182,7 +9143,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>15</v>
@@ -9194,22 +9155,22 @@
         <v>30</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>24</v>
@@ -9226,7 +9187,7 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>15</v>
@@ -9238,10 +9199,10 @@
         <v>30</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>20</v>
@@ -9256,7 +9217,7 @@
         <v>136</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="L150" s="2" t="s">
         <v>25</v>
@@ -9270,7 +9231,7 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>15</v>
@@ -9282,10 +9243,10 @@
         <v>17</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>20</v>
@@ -9297,10 +9258,10 @@
         <v>22</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>25</v>
@@ -9314,7 +9275,7 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>15</v>
@@ -9326,25 +9287,25 @@
         <v>30</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>596</v>
+        <v>24</v>
       </c>
       <c r="L152" s="2" t="s">
         <v>25</v>
@@ -9358,7 +9319,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>15</v>
@@ -9370,10 +9331,10 @@
         <v>17</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>39</v>
@@ -9385,10 +9346,10 @@
         <v>22</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L153" s="2" t="s">
         <v>25</v>
@@ -9402,7 +9363,7 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>15</v>
@@ -9414,22 +9375,22 @@
         <v>30</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I154" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>24</v>
@@ -9446,7 +9407,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>15</v>
@@ -9458,22 +9419,22 @@
         <v>30</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="I155" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>24</v>
@@ -9490,7 +9451,7 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>15</v>
@@ -9502,10 +9463,10 @@
         <v>30</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>20</v>
@@ -9517,7 +9478,7 @@
         <v>22</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>239</v>
@@ -9534,7 +9495,7 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>15</v>
@@ -9546,22 +9507,22 @@
         <v>30</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>24</v>
@@ -9573,7 +9534,7 @@
         <v>35</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
@@ -9590,7 +9551,7 @@
         <v>30</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>47</v>
@@ -9622,7 +9583,7 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>15</v>
@@ -9634,25 +9595,25 @@
         <v>30</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>225</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>59</v>
@@ -9666,7 +9627,7 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>15</v>
@@ -9678,22 +9639,22 @@
         <v>30</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="I160" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>24</v>
@@ -9710,7 +9671,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>15</v>
@@ -9722,22 +9683,22 @@
         <v>30</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="I161" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>24</v>
@@ -9754,7 +9715,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>15</v>
@@ -9766,10 +9727,10 @@
         <v>30</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>20</v>
@@ -9781,7 +9742,7 @@
         <v>22</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>137</v>
@@ -9793,12 +9754,12 @@
         <v>35</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>15</v>
@@ -9810,22 +9771,22 @@
         <v>30</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I163" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>47</v>
@@ -9837,12 +9798,12 @@
         <v>49</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>15</v>
@@ -9854,10 +9815,10 @@
         <v>30</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>39</v>
@@ -9869,10 +9830,10 @@
         <v>22</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>555</v>
+        <v>290</v>
       </c>
       <c r="L164" s="2" t="s">
         <v>25</v>
@@ -9886,7 +9847,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>15</v>
@@ -9898,25 +9859,25 @@
         <v>30</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="I165" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="L165" s="2" t="s">
         <v>25</v>
@@ -9925,12 +9886,12 @@
         <v>92</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>15</v>
@@ -9942,10 +9903,10 @@
         <v>30</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>39</v>
@@ -9974,7 +9935,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>15</v>
@@ -9983,25 +9944,25 @@
         <v>29</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>650</v>
+        <v>47</v>
       </c>
       <c r="K167" s="2" t="s">
         <v>47</v>
@@ -10013,12 +9974,12 @@
         <v>35</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>15</v>
@@ -10030,22 +9991,22 @@
         <v>30</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="I168" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K168" s="2" t="s">
         <v>143</v>
@@ -10062,7 +10023,7 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>15</v>
@@ -10071,25 +10032,25 @@
         <v>29</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>658</v>
+        <v>47</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>355</v>
+        <v>47</v>
       </c>
       <c r="K169" s="2" t="s">
         <v>47</v>
@@ -10098,15 +10059,15 @@
         <v>59</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>15</v>
@@ -10118,25 +10079,25 @@
         <v>30</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="F170" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H170" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G170" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H170" s="2" t="s">
+      <c r="I170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I170" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J170" s="2" t="s">
+      <c r="K170" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="K170" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>25</v>
@@ -10150,7 +10111,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>15</v>
@@ -10162,22 +10123,22 @@
         <v>30</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="I171" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K171" s="2" t="s">
         <v>24</v>
@@ -10194,7 +10155,7 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>15</v>
@@ -10206,16 +10167,16 @@
         <v>30</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>225</v>
@@ -10238,7 +10199,7 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>15</v>
@@ -10250,16 +10211,16 @@
         <v>30</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>22</v>
@@ -10268,7 +10229,7 @@
         <v>125</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>25</v>
@@ -10282,7 +10243,7 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>15</v>
@@ -10294,16 +10255,16 @@
         <v>30</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>22</v>
@@ -10312,7 +10273,7 @@
         <v>125</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>25</v>
@@ -10326,7 +10287,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>15</v>
@@ -10335,25 +10296,25 @@
         <v>29</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>47</v>
@@ -10362,15 +10323,15 @@
         <v>59</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>15</v>
@@ -10382,10 +10343,10 @@
         <v>47</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>20</v>
@@ -10414,7 +10375,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>15</v>
@@ -10426,10 +10387,10 @@
         <v>208</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>39</v>
@@ -10458,7 +10419,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>15</v>
@@ -10470,22 +10431,22 @@
         <v>30</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="I178" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="K178" s="2" t="s">
         <v>24</v>
@@ -10502,7 +10463,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>15</v>
@@ -10514,10 +10475,10 @@
         <v>47</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>39</v>
@@ -10546,7 +10507,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>15</v>
@@ -10558,10 +10519,10 @@
         <v>47</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>39</v>
@@ -10590,7 +10551,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>15</v>
@@ -10602,10 +10563,10 @@
         <v>47</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>20</v>
@@ -10634,7 +10595,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>15</v>
@@ -10643,25 +10604,25 @@
         <v>29</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>249</v>
+        <v>47</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>47</v>
@@ -10670,15 +10631,15 @@
         <v>144</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>15</v>
@@ -10690,10 +10651,10 @@
         <v>30</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>20</v>
@@ -10705,7 +10666,7 @@
         <v>225</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="K183" s="2" t="s">
         <v>47</v>
@@ -10722,7 +10683,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>15</v>
@@ -10734,10 +10695,10 @@
         <v>17</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>20</v>
@@ -10749,7 +10710,7 @@
         <v>22</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>277</v>
+        <v>168</v>
       </c>
       <c r="K184" s="2" t="s">
         <v>24</v>
@@ -10766,7 +10727,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>15</v>
@@ -10778,22 +10739,22 @@
         <v>30</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="K185" s="2" t="s">
         <v>47</v>
@@ -10805,12 +10766,12 @@
         <v>49</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>15</v>
@@ -10822,25 +10783,25 @@
         <v>30</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L186" s="2" t="s">
         <v>25</v>
@@ -10854,7 +10815,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>15</v>
@@ -10866,25 +10827,25 @@
         <v>30</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>144</v>
@@ -10898,7 +10859,7 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>15</v>
@@ -10910,25 +10871,25 @@
         <v>30</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I188" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L188" s="2" t="s">
         <v>25</v>
@@ -10942,7 +10903,7 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>15</v>
@@ -10954,25 +10915,25 @@
         <v>30</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I189" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="L189" s="2" t="s">
         <v>144</v>
@@ -10986,7 +10947,7 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>15</v>
@@ -10998,10 +10959,10 @@
         <v>30</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>20</v>
@@ -11013,7 +10974,7 @@
         <v>22</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>91</v>
+        <v>695</v>
       </c>
       <c r="K190" s="2" t="s">
         <v>24</v>
@@ -11030,7 +10991,7 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>15</v>
@@ -11042,10 +11003,10 @@
         <v>30</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>39</v>
@@ -11057,10 +11018,10 @@
         <v>22</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L191" s="2" t="s">
         <v>25</v>
@@ -11086,7 +11047,7 @@
         <v>30</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>47</v>
@@ -11151,7 +11112,7 @@
         <v>47</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="M193" s="2" t="s">
         <v>49</v>
@@ -11195,7 +11156,7 @@
         <v>47</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="M194" s="2" t="s">
         <v>92</v>
@@ -11206,7 +11167,7 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>15</v>
@@ -11218,28 +11179,28 @@
         <v>30</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I195" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="M195" s="2" t="s">
         <v>49</v>
@@ -11261,23 +11222,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="B2" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D2" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E2" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -11285,16 +11246,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -11302,7 +11263,7 @@
         <v>194</v>
       </c>
       <c r="D5" s="5">
-        <v>0.005154639175257732</v>
+        <v>0.010309278350515464</v>
       </c>
       <c r="G5" s="4">
         <v>8.04</v>
@@ -11313,7 +11274,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -11334,7 +11295,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -11365,12 +11326,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="B2">
         <v>194</v>
@@ -11378,7 +11339,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.005154639175257732</v>
+        <v>0.010309278350515464</v>
       </c>
       <c r="B5" s="7"/>
     </row>
@@ -11394,25 +11355,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -11429,16 +11390,16 @@
         <v>172</v>
       </c>
       <c r="G10" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -11450,7 +11411,7 @@
         <v>49</v>
       </c>
       <c r="Q10">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -11467,10 +11428,10 @@
         <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="K11">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M11" t="s">
         <v>59</v>
@@ -11482,7 +11443,7 @@
         <v>26</v>
       </c>
       <c r="Q11">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -11499,7 +11460,7 @@
         <v>132</v>
       </c>
       <c r="M12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -11508,7 +11469,7 @@
         <v>35</v>
       </c>
       <c r="Q12">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -11519,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -11534,12 +11495,12 @@
         <v>92</v>
       </c>
       <c r="Q13">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -11550,16 +11511,10 @@
       <c r="N14">
         <v>13</v>
       </c>
-      <c r="P14" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q14">
-        <v>31</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -11567,7 +11522,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="N16">
         <v>3</v>
@@ -11575,7 +11530,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -11583,7 +11538,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -11594,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -11608,7 +11563,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>37</v>
@@ -11616,49 +11571,49 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2">
+        <v>563</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="2">
-        <v>568</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
@@ -11667,77 +11622,77 @@
         <v>458</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
